--- a/Control.xlsx
+++ b/Control.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sigma_pruebas1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCC9387-7167-43AC-8481-2D9F7F187B50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA29665-E921-4F16-A735-ADF6D91C79BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
-  <si>
-    <t>ac-ca22.jsp</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -216,9 +213,6 @@
     <t>obtfedg.jsp</t>
   </si>
   <si>
-    <t>obtgeo_ac-ca22.jsp</t>
-  </si>
-  <si>
     <t>obtgeo_aupr.jsp</t>
   </si>
   <si>
@@ -276,9 +270,6 @@
     <t>obtpassdg.jsp</t>
   </si>
   <si>
-    <t>obtregsap.jsp (3 matches)</t>
-  </si>
-  <si>
     <t>opcion.jsp</t>
   </si>
   <si>
@@ -427,6 +418,240 @@
   </si>
   <si>
     <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>ac-eic25.jsp</t>
+  </si>
+  <si>
+    <t>adescarga.jsp</t>
+  </si>
+  <si>
+    <t>ajaxjs.js</t>
+  </si>
+  <si>
+    <t>amapa.html</t>
+  </si>
+  <si>
+    <t>astyle.css</t>
+  </si>
+  <si>
+    <t>avance_act_mg.html</t>
+  </si>
+  <si>
+    <t>avance_precarta20_carta.jsp</t>
+  </si>
+  <si>
+    <t>avance_preedo.jsp</t>
+  </si>
+  <si>
+    <t>avance_valoc.jsp</t>
+  </si>
+  <si>
+    <t>avance_vermapa.jsp</t>
+  </si>
+  <si>
+    <t>avance.html</t>
+  </si>
+  <si>
+    <t>avance.jsp</t>
+  </si>
+  <si>
+    <t>blob.html</t>
+  </si>
+  <si>
+    <t>borra_mark.jsp</t>
+  </si>
+  <si>
+    <t>capas_ce.html</t>
+  </si>
+  <si>
+    <t>capas_pre.html</t>
+  </si>
+  <si>
+    <t>capas.html</t>
+  </si>
+  <si>
+    <t>capasapoyo.jsp</t>
+  </si>
+  <si>
+    <t>descargazip.jsp</t>
+  </si>
+  <si>
+    <t>EPS32800.js</t>
+  </si>
+  <si>
+    <t>EPS6365.js</t>
+  </si>
+  <si>
+    <t>exp_csv.jsp</t>
+  </si>
+  <si>
+    <t>exp_dbf.jsp</t>
+  </si>
+  <si>
+    <t>exporta.bat</t>
+  </si>
+  <si>
+    <t>funciones_especiales.js</t>
+  </si>
+  <si>
+    <t>google1.jsp</t>
+  </si>
+  <si>
+    <t>Guía metodológica para la revisión e integración de la ACI a la BC del MG_feb25.pdf</t>
+  </si>
+  <si>
+    <t>imprime.jsp</t>
+  </si>
+  <si>
+    <t>index2.jsp</t>
+  </si>
+  <si>
+    <t>inegiview_dentro.html</t>
+  </si>
+  <si>
+    <t>inegiview.html</t>
+  </si>
+  <si>
+    <t>js_agebu.js</t>
+  </si>
+  <si>
+    <t>js_caserios.js</t>
+  </si>
+  <si>
+    <t>js_localidades.js</t>
+  </si>
+  <si>
+    <t>js_manzanas.js</t>
+  </si>
+  <si>
+    <t>js_polext.js</t>
+  </si>
+  <si>
+    <t>js_polrur.js</t>
+  </si>
+  <si>
+    <t>js_predig.js</t>
+  </si>
+  <si>
+    <t>mapate.jsp</t>
+  </si>
+  <si>
+    <t>mapatedesc.jsp</t>
+  </si>
+  <si>
+    <t>MD5.js</t>
+  </si>
+  <si>
+    <t>menu_reporte.css</t>
+  </si>
+  <si>
+    <t>mod_casosCd.jsp</t>
+  </si>
+  <si>
+    <t>mostrar_qr.jsp</t>
+  </si>
+  <si>
+    <t>mousecount.jsp</t>
+  </si>
+  <si>
+    <t>obt_inegipoint_video.jsp</t>
+  </si>
+  <si>
+    <t>obtalt.jsp</t>
+  </si>
+  <si>
+    <t>obtcoord.jsp</t>
+  </si>
+  <si>
+    <t>obtgeo_ac-eic25.jsp</t>
+  </si>
+  <si>
+    <t>obtgeo_loc_baja.jsp</t>
+  </si>
+  <si>
+    <t>obtgeo_mz_baja.jsp</t>
+  </si>
+  <si>
+    <t>obtgeo_tefr.jsp</t>
+  </si>
+  <si>
+    <t>obtregsap.jsp</t>
+  </si>
+  <si>
+    <t>open_server.sublime-project</t>
+  </si>
+  <si>
+    <t>open_server.sublime-workspace</t>
+  </si>
+  <si>
+    <t>openlayers2.sublime-project</t>
+  </si>
+  <si>
+    <t>openlayers2.sublime-workspace</t>
+  </si>
+  <si>
+    <t>popcalendar.js</t>
+  </si>
+  <si>
+    <t>proj4js.js</t>
+  </si>
+  <si>
+    <t>qrcode.min.js</t>
+  </si>
+  <si>
+    <t>reg_repmun.jsp</t>
+  </si>
+  <si>
+    <t>regcoord.jsp</t>
+  </si>
+  <si>
+    <t>regresa.jsp</t>
+  </si>
+  <si>
+    <t>Simplificar_caserios.pdf</t>
+  </si>
+  <si>
+    <t>streetview_dentro.html</t>
+  </si>
+  <si>
+    <t>streetview.html</t>
+  </si>
+  <si>
+    <t>style.css</t>
+  </si>
+  <si>
+    <t>swipe.html</t>
+  </si>
+  <si>
+    <t>todo.js</t>
+  </si>
+  <si>
+    <t>vercodigoJ.jsp</t>
+  </si>
+  <si>
+    <t>vermanuales.jsp</t>
+  </si>
+  <si>
+    <t>verobs.jsp</t>
+  </si>
+  <si>
+    <t>verobsmzvalpe.jsp</t>
+  </si>
+  <si>
+    <t>verservers.jsp</t>
+  </si>
+  <si>
+    <t>vershape.jsp</t>
+  </si>
+  <si>
+    <t>video.jsp</t>
+  </si>
+  <si>
+    <t>zedit-pass.jsp</t>
+  </si>
+  <si>
+    <t>zedit-passSigma.jsp</t>
   </si>
 </sst>
 </file>
@@ -511,7 +736,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -526,6 +751,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -843,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CFB12C-C000-4D62-A088-E6A986C2EDDD}">
-  <dimension ref="B1:G129"/>
+  <dimension ref="B1:G204"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
@@ -855,1049 +1083,1423 @@
   <sheetData>
     <row r="1" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>131</v>
+      </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="6"/>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="7"/>
     </row>
     <row r="18" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
+      <c r="E20" s="7"/>
     </row>
     <row r="21" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
+      <c r="E21" s="7"/>
     </row>
     <row r="22" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="4"/>
+      <c r="E24" s="7"/>
     </row>
     <row r="25" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="4"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
+      <c r="E34" s="7"/>
     </row>
     <row r="35" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="4"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="7"/>
     </row>
     <row r="37" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="7"/>
     </row>
     <row r="38" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="39" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="7"/>
     </row>
     <row r="40" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="7"/>
     </row>
     <row r="41" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="5"/>
-      <c r="E41" s="4"/>
+      <c r="E41" s="7"/>
     </row>
     <row r="42" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="7"/>
     </row>
     <row r="43" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="4"/>
+      <c r="E43" s="7"/>
     </row>
     <row r="44" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="7"/>
     </row>
     <row r="45" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="5"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="7"/>
     </row>
     <row r="46" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="4"/>
+      <c r="E46" s="7"/>
     </row>
     <row r="47" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="5"/>
-      <c r="E47" s="4"/>
+      <c r="E47" s="7"/>
     </row>
     <row r="48" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="4"/>
+      <c r="E48" s="7"/>
     </row>
     <row r="49" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="7"/>
     </row>
     <row r="50" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="4"/>
+      <c r="E50" s="7"/>
     </row>
     <row r="51" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="7"/>
     </row>
     <row r="52" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="4"/>
+      <c r="E52" s="7"/>
     </row>
     <row r="53" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="4"/>
+      <c r="E53" s="7"/>
     </row>
     <row r="54" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="7"/>
     </row>
     <row r="55" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="4"/>
+      <c r="E55" s="7"/>
     </row>
     <row r="56" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="4"/>
+      <c r="E56" s="7"/>
     </row>
     <row r="57" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="7"/>
     </row>
     <row r="58" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="4"/>
+      <c r="E58" s="7"/>
     </row>
     <row r="59" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="4"/>
+      <c r="E59" s="7"/>
     </row>
     <row r="60" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="4"/>
+      <c r="E60" s="7"/>
     </row>
     <row r="61" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C61" s="4"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="4"/>
+      <c r="E61" s="7"/>
     </row>
     <row r="62" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="C62" s="4"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="4"/>
+      <c r="E62" s="7"/>
     </row>
     <row r="63" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="4"/>
+      <c r="E63" s="7"/>
     </row>
     <row r="64" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="C64" s="4"/>
       <c r="D64" s="5"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="7"/>
     </row>
     <row r="65" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="5"/>
-      <c r="E65" s="4"/>
+      <c r="E65" s="7"/>
     </row>
     <row r="66" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="5"/>
-      <c r="E66" s="4"/>
+      <c r="E66" s="7"/>
     </row>
     <row r="67" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="5"/>
-      <c r="E67" s="4"/>
+      <c r="E67" s="7"/>
     </row>
     <row r="68" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="4" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="5"/>
-      <c r="E68" s="4"/>
+      <c r="E68" s="7"/>
     </row>
     <row r="69" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="4" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="5"/>
-      <c r="E69" s="4"/>
+      <c r="E69" s="7"/>
     </row>
     <row r="70" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="4" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="5"/>
-      <c r="E70" s="4"/>
+      <c r="E70" s="7"/>
     </row>
     <row r="71" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="4" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="4"/>
+      <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="4"/>
+      <c r="E72" s="7"/>
     </row>
     <row r="73" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="4" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="4"/>
+      <c r="E73" s="7"/>
     </row>
     <row r="74" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="4"/>
+      <c r="E74" s="7"/>
     </row>
     <row r="75" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="4" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="4"/>
+      <c r="E75" s="7"/>
     </row>
     <row r="76" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="4" t="s">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="4"/>
+      <c r="E76" s="7"/>
     </row>
     <row r="77" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="4" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="4"/>
+      <c r="E77" s="7"/>
     </row>
     <row r="78" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="4"/>
+      <c r="E78" s="7"/>
     </row>
     <row r="79" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="5"/>
-      <c r="E79" s="4"/>
+      <c r="E79" s="7"/>
     </row>
     <row r="80" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="4" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="4"/>
+      <c r="E80" s="7"/>
     </row>
     <row r="81" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C81" s="4"/>
       <c r="D81" s="5"/>
-      <c r="E81" s="4"/>
+      <c r="E81" s="7"/>
     </row>
     <row r="82" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C82" s="4"/>
       <c r="D82" s="5"/>
-      <c r="E82" s="4"/>
+      <c r="E82" s="7"/>
     </row>
     <row r="83" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="4" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="C83" s="4"/>
       <c r="D83" s="5"/>
-      <c r="E83" s="4"/>
+      <c r="E83" s="7"/>
     </row>
     <row r="84" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="4" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="5"/>
-      <c r="E84" s="4"/>
+      <c r="E84" s="7"/>
     </row>
     <row r="85" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="5"/>
-      <c r="E85" s="4"/>
+      <c r="E85" s="7"/>
     </row>
     <row r="86" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="4" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="5"/>
-      <c r="E86" s="4"/>
+      <c r="E86" s="7"/>
     </row>
     <row r="87" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="4" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="5"/>
-      <c r="E87" s="4"/>
+      <c r="E87" s="7"/>
     </row>
     <row r="88" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="4" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="5"/>
-      <c r="E88" s="4"/>
+      <c r="E88" s="7"/>
     </row>
     <row r="89" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="5"/>
-      <c r="E89" s="4"/>
+      <c r="E89" s="7"/>
     </row>
     <row r="90" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="4" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="5"/>
-      <c r="E90" s="4"/>
+      <c r="E90" s="7"/>
     </row>
     <row r="91" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="4" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="5"/>
-      <c r="E91" s="4"/>
+      <c r="E91" s="7"/>
     </row>
     <row r="92" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="4" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="5"/>
-      <c r="E92" s="4"/>
+      <c r="E92" s="7"/>
     </row>
     <row r="93" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="5"/>
-      <c r="E93" s="4"/>
+      <c r="E93" s="7"/>
     </row>
     <row r="94" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="5"/>
-      <c r="E94" s="4"/>
+      <c r="E94" s="7"/>
     </row>
     <row r="95" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="4" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="5"/>
-      <c r="E95" s="4"/>
+      <c r="E95" s="7"/>
     </row>
     <row r="96" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="5"/>
-      <c r="E96" s="4"/>
+      <c r="E96" s="7"/>
     </row>
     <row r="97" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="5"/>
-      <c r="E97" s="4"/>
+      <c r="E97" s="7"/>
     </row>
     <row r="98" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="4" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="5"/>
-      <c r="E98" s="4"/>
+      <c r="E98" s="7"/>
     </row>
     <row r="99" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="5"/>
-      <c r="E99" s="4"/>
+      <c r="E99" s="7"/>
     </row>
     <row r="100" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="4" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="5"/>
-      <c r="E100" s="4"/>
+      <c r="E100" s="7"/>
     </row>
     <row r="101" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="4" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="5"/>
-      <c r="E101" s="4"/>
+      <c r="E101" s="7"/>
     </row>
     <row r="102" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="4" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="5"/>
-      <c r="E102" s="4"/>
+      <c r="E102" s="7"/>
     </row>
     <row r="103" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="4" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="5"/>
-      <c r="E103" s="4"/>
+      <c r="E103" s="7"/>
     </row>
     <row r="104" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="4" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="5"/>
-      <c r="E104" s="4"/>
+      <c r="E104" s="7"/>
     </row>
     <row r="105" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="4" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="5"/>
-      <c r="E105" s="4"/>
+      <c r="E105" s="7"/>
     </row>
     <row r="106" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="4" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="5"/>
-      <c r="E106" s="4"/>
+      <c r="E106" s="7"/>
     </row>
     <row r="107" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="4" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="5"/>
-      <c r="E107" s="4"/>
+      <c r="E107" s="7"/>
     </row>
     <row r="108" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="5"/>
-      <c r="E108" s="4"/>
+      <c r="E108" s="7"/>
     </row>
     <row r="109" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="4" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="5"/>
-      <c r="E109" s="4"/>
+      <c r="E109" s="7"/>
     </row>
     <row r="110" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="4" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="5"/>
-      <c r="E110" s="4"/>
+      <c r="E110" s="7"/>
     </row>
     <row r="111" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="4" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="5"/>
-      <c r="E111" s="4"/>
+      <c r="E111" s="7"/>
     </row>
     <row r="112" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="4" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="5"/>
-      <c r="E112" s="4"/>
+      <c r="E112" s="7"/>
     </row>
     <row r="113" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="4" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="5"/>
-      <c r="E113" s="4"/>
+      <c r="E113" s="7"/>
     </row>
     <row r="114" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="4" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="5"/>
-      <c r="E114" s="4"/>
+      <c r="E114" s="7"/>
     </row>
     <row r="115" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="4" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="5"/>
-      <c r="E115" s="4"/>
+      <c r="E115" s="7"/>
     </row>
     <row r="116" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="4" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="5"/>
-      <c r="E116" s="4"/>
+      <c r="E116" s="7"/>
     </row>
     <row r="117" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="4" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="5"/>
-      <c r="E117" s="4"/>
+      <c r="E117" s="7"/>
     </row>
     <row r="118" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="4" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C118" s="4"/>
       <c r="D118" s="5"/>
-      <c r="E118" s="4"/>
+      <c r="E118" s="7"/>
     </row>
     <row r="119" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="4" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="5"/>
-      <c r="E119" s="4"/>
+      <c r="E119" s="7"/>
     </row>
     <row r="120" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="4" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="5"/>
-      <c r="E120" s="4"/>
+      <c r="E120" s="7"/>
     </row>
     <row r="121" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="4" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="C121" s="4"/>
       <c r="D121" s="5"/>
-      <c r="E121" s="4"/>
+      <c r="E121" s="7"/>
     </row>
     <row r="122" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="4" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C122" s="4"/>
       <c r="D122" s="5"/>
-      <c r="E122" s="4"/>
+      <c r="E122" s="7"/>
     </row>
     <row r="123" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="5"/>
-      <c r="E123" s="4"/>
+      <c r="E123" s="7"/>
     </row>
     <row r="124" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="4" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="5"/>
-      <c r="E124" s="4"/>
+      <c r="E124" s="7"/>
     </row>
     <row r="125" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="4" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="5"/>
-      <c r="E125" s="4"/>
+      <c r="E125" s="7"/>
     </row>
     <row r="126" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="5"/>
-      <c r="E126" s="4"/>
+      <c r="E126" s="7"/>
     </row>
     <row r="127" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="4" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="5"/>
-      <c r="E127" s="4"/>
+      <c r="E127" s="7"/>
     </row>
     <row r="128" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="5"/>
-      <c r="E128" s="4"/>
+      <c r="E128" s="7"/>
     </row>
     <row r="129" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="5"/>
-      <c r="E129" s="4"/>
+      <c r="E129" s="7"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" t="s">
+        <v>208</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sigma_pruebas1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA29665-E921-4F16-A735-ADF6D91C79BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526BABFF-BB27-4798-BE81-221A2BF88BC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
@@ -432,9 +432,6 @@
     <t>amapa.html</t>
   </si>
   <si>
-    <t>astyle.css</t>
-  </si>
-  <si>
     <t>avance_act_mg.html</t>
   </si>
   <si>
@@ -652,6 +649,9 @@
   </si>
   <si>
     <t>zedit-passSigma.jsp</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
   </si>
 </sst>
 </file>
@@ -736,7 +736,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -754,6 +754,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1071,10 +1074,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CFB12C-C000-4D62-A088-E6A986C2EDDD}">
-  <dimension ref="B1:G204"/>
+  <dimension ref="B1:G208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="42.140625" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
     <col min="4" max="4" width="22.85546875" customWidth="1"/>
     <col min="5" max="5" width="24.5703125" customWidth="1"/>
@@ -1105,7 +1108,10 @@
       <c r="B2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E2" s="7"/>
       <c r="F2" s="6"/>
       <c r="G2" s="2"/>
@@ -1168,7 +1174,7 @@
     </row>
     <row r="10" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="5"/>
@@ -1176,7 +1182,7 @@
     </row>
     <row r="11" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="5"/>
@@ -1184,7 +1190,7 @@
     </row>
     <row r="12" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="5"/>
@@ -1192,7 +1198,7 @@
     </row>
     <row r="13" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="5"/>
@@ -1200,7 +1206,7 @@
     </row>
     <row r="14" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="5"/>
@@ -1208,7 +1214,7 @@
     </row>
     <row r="15" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="5"/>
@@ -1216,7 +1222,7 @@
     </row>
     <row r="16" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
@@ -1224,7 +1230,7 @@
     </row>
     <row r="17" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="5"/>
@@ -1232,7 +1238,7 @@
     </row>
     <row r="18" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="5"/>
@@ -1240,7 +1246,7 @@
     </row>
     <row r="19" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="5"/>
@@ -1248,7 +1254,7 @@
     </row>
     <row r="20" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="5"/>
@@ -1256,7 +1262,7 @@
     </row>
     <row r="21" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="5"/>
@@ -1264,7 +1270,7 @@
     </row>
     <row r="22" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="5"/>
@@ -1272,7 +1278,7 @@
     </row>
     <row r="23" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="5"/>
@@ -1280,7 +1286,7 @@
     </row>
     <row r="24" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="5"/>
@@ -1288,7 +1294,7 @@
     </row>
     <row r="25" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="5"/>
@@ -1296,7 +1302,7 @@
     </row>
     <row r="26" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
@@ -1312,7 +1318,7 @@
     </row>
     <row r="28" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5"/>
@@ -1320,7 +1326,7 @@
     </row>
     <row r="29" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="5"/>
@@ -1328,7 +1334,7 @@
     </row>
     <row r="30" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
@@ -1368,7 +1374,7 @@
     </row>
     <row r="35" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="5"/>
@@ -1376,7 +1382,7 @@
     </row>
     <row r="36" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="5"/>
@@ -1384,7 +1390,7 @@
     </row>
     <row r="37" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="5"/>
@@ -1392,7 +1398,7 @@
     </row>
     <row r="38" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="5"/>
@@ -1424,7 +1430,7 @@
     </row>
     <row r="42" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="5"/>
@@ -1432,7 +1438,7 @@
     </row>
     <row r="43" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="5"/>
@@ -1440,7 +1446,7 @@
     </row>
     <row r="44" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="5"/>
@@ -1448,7 +1454,7 @@
     </row>
     <row r="45" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="5"/>
@@ -1456,7 +1462,7 @@
     </row>
     <row r="46" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="5"/>
@@ -1464,7 +1470,7 @@
     </row>
     <row r="47" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="5"/>
@@ -1472,7 +1478,7 @@
     </row>
     <row r="48" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="5"/>
@@ -1480,7 +1486,7 @@
     </row>
     <row r="49" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="5"/>
@@ -1536,15 +1542,15 @@
     </row>
     <row r="56" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="5"/>
       <c r="E56" s="7"/>
     </row>
     <row r="57" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="4" t="s">
-        <v>29</v>
+      <c r="B57" s="8" t="s">
+        <v>156</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="5"/>
@@ -1560,7 +1566,7 @@
     </row>
     <row r="59" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="5"/>
@@ -1568,7 +1574,7 @@
     </row>
     <row r="60" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="5"/>
@@ -1576,7 +1582,7 @@
     </row>
     <row r="61" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="C61" s="4"/>
       <c r="D61" s="5"/>
@@ -1656,7 +1662,7 @@
     </row>
     <row r="71" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="4" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="5"/>
@@ -1664,7 +1670,7 @@
     </row>
     <row r="72" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="5"/>
@@ -1680,7 +1686,7 @@
     </row>
     <row r="74" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
-        <v>170</v>
+        <v>33</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="5"/>
@@ -1688,7 +1694,7 @@
     </row>
     <row r="75" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="4" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="5"/>
@@ -1704,7 +1710,7 @@
     </row>
     <row r="77" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="4" t="s">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="5"/>
@@ -1712,7 +1718,7 @@
     </row>
     <row r="78" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="5"/>
@@ -1720,7 +1726,7 @@
     </row>
     <row r="79" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="5"/>
@@ -1728,7 +1734,7 @@
     </row>
     <row r="80" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="4" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="5"/>
@@ -1736,7 +1742,7 @@
     </row>
     <row r="81" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C81" s="4"/>
       <c r="D81" s="5"/>
@@ -1744,7 +1750,7 @@
     </row>
     <row r="82" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C82" s="4"/>
       <c r="D82" s="5"/>
@@ -1752,7 +1758,7 @@
     </row>
     <row r="83" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C83" s="4"/>
       <c r="D83" s="5"/>
@@ -1760,7 +1766,7 @@
     </row>
     <row r="84" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="5"/>
@@ -1768,7 +1774,7 @@
     </row>
     <row r="85" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="5"/>
@@ -1776,7 +1782,7 @@
     </row>
     <row r="86" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="5"/>
@@ -1784,7 +1790,7 @@
     </row>
     <row r="87" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="5"/>
@@ -1792,7 +1798,7 @@
     </row>
     <row r="88" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="5"/>
@@ -1800,7 +1806,7 @@
     </row>
     <row r="89" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="5"/>
@@ -1808,7 +1814,7 @@
     </row>
     <row r="90" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="5"/>
@@ -1816,7 +1822,7 @@
     </row>
     <row r="91" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="5"/>
@@ -1824,7 +1830,7 @@
     </row>
     <row r="92" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="5"/>
@@ -1832,7 +1838,7 @@
     </row>
     <row r="93" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="5"/>
@@ -1840,7 +1846,7 @@
     </row>
     <row r="94" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="5"/>
@@ -1848,7 +1854,7 @@
     </row>
     <row r="95" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="5"/>
@@ -1856,7 +1862,7 @@
     </row>
     <row r="96" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="5"/>
@@ -1864,7 +1870,7 @@
     </row>
     <row r="97" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="5"/>
@@ -1872,7 +1878,7 @@
     </row>
     <row r="98" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="4" t="s">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="5"/>
@@ -1880,7 +1886,7 @@
     </row>
     <row r="99" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="5"/>
@@ -1888,7 +1894,7 @@
     </row>
     <row r="100" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="4" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="5"/>
@@ -1896,7 +1902,7 @@
     </row>
     <row r="101" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="4" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="5"/>
@@ -1904,7 +1910,7 @@
     </row>
     <row r="102" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="4" t="s">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="5"/>
@@ -1912,7 +1918,7 @@
     </row>
     <row r="103" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="4" t="s">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="5"/>
@@ -1920,7 +1926,7 @@
     </row>
     <row r="104" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="5"/>
@@ -1928,7 +1934,7 @@
     </row>
     <row r="105" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="4" t="s">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="5"/>
@@ -1944,7 +1950,7 @@
     </row>
     <row r="107" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="4" t="s">
-        <v>178</v>
+        <v>58</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="5"/>
@@ -1952,7 +1958,7 @@
     </row>
     <row r="108" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="5"/>
@@ -1960,7 +1966,7 @@
     </row>
     <row r="109" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="5"/>
@@ -1968,7 +1974,7 @@
     </row>
     <row r="110" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="5"/>
@@ -1976,7 +1982,7 @@
     </row>
     <row r="111" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="4" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="5"/>
@@ -1984,7 +1990,7 @@
     </row>
     <row r="112" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="4" t="s">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="5"/>
@@ -1992,7 +1998,7 @@
     </row>
     <row r="113" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="5"/>
@@ -2000,7 +2006,7 @@
     </row>
     <row r="114" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="4" t="s">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="5"/>
@@ -2008,7 +2014,7 @@
     </row>
     <row r="115" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="4" t="s">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="5"/>
@@ -2016,7 +2022,7 @@
     </row>
     <row r="116" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="5"/>
@@ -2024,7 +2030,7 @@
     </row>
     <row r="117" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="5"/>
@@ -2032,7 +2038,7 @@
     </row>
     <row r="118" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C118" s="4"/>
       <c r="D118" s="5"/>
@@ -2040,7 +2046,7 @@
     </row>
     <row r="119" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="4" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="5"/>
@@ -2048,7 +2054,7 @@
     </row>
     <row r="120" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="4" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="5"/>
@@ -2056,7 +2062,7 @@
     </row>
     <row r="121" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C121" s="4"/>
       <c r="D121" s="5"/>
@@ -2064,7 +2070,7 @@
     </row>
     <row r="122" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C122" s="4"/>
       <c r="D122" s="5"/>
@@ -2072,7 +2078,7 @@
     </row>
     <row r="123" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="5"/>
@@ -2080,7 +2086,7 @@
     </row>
     <row r="124" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="4" t="s">
-        <v>71</v>
+        <v>181</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="5"/>
@@ -2088,7 +2094,7 @@
     </row>
     <row r="125" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="4" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="5"/>
@@ -2096,7 +2102,7 @@
     </row>
     <row r="126" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="5"/>
@@ -2104,7 +2110,7 @@
     </row>
     <row r="127" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="5"/>
@@ -2112,7 +2118,7 @@
     </row>
     <row r="128" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="5"/>
@@ -2120,389 +2126,621 @@
     </row>
     <row r="129" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="5"/>
-      <c r="E129" s="7"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" t="s">
+      <c r="E129" s="4"/>
+    </row>
+    <row r="130" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B132" t="s">
+      <c r="C130" s="4"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="4"/>
+    </row>
+    <row r="131" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B133" t="s">
+      <c r="C131" s="4"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="4"/>
+    </row>
+    <row r="132" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" t="s">
+      <c r="C132" s="4"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="4"/>
+    </row>
+    <row r="133" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B135" t="s">
+      <c r="C133" s="4"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="4"/>
+    </row>
+    <row r="134" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C134" s="4"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="4"/>
+    </row>
+    <row r="135" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="4"/>
+    </row>
+    <row r="136" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="4" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B136" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B137" t="s">
+      <c r="C136" s="4"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="4"/>
+    </row>
+    <row r="137" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
+      <c r="C137" s="4"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="4"/>
+    </row>
+    <row r="138" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B139" t="s">
+      <c r="C138" s="4"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="4"/>
+    </row>
+    <row r="139" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="4" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B140" t="s">
+      <c r="C139" s="4"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="4"/>
+    </row>
+    <row r="140" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C140" s="4"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="4"/>
+    </row>
+    <row r="141" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C141" s="4"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="4"/>
+    </row>
+    <row r="142" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="4" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B141" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B142" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
+      <c r="C142" s="4"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="4"/>
+    </row>
+    <row r="143" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="4" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
+      <c r="C143" s="4"/>
+      <c r="D143" s="5"/>
+      <c r="E143" s="4"/>
+    </row>
+    <row r="144" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="4" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B145" t="s">
+      <c r="C144" s="4"/>
+      <c r="D144" s="5"/>
+      <c r="E144" s="4"/>
+    </row>
+    <row r="145" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="4"/>
+    </row>
+    <row r="146" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C146" s="4"/>
+      <c r="D146" s="5"/>
+      <c r="E146" s="4"/>
+    </row>
+    <row r="147" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C147" s="4"/>
+      <c r="D147" s="5"/>
+      <c r="E147" s="4"/>
+    </row>
+    <row r="148" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C148" s="4"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="4"/>
+    </row>
+    <row r="149" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="4" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B146" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B148" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B149" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B150" t="s">
+      <c r="C149" s="4"/>
+      <c r="D149" s="5"/>
+      <c r="E149" s="4"/>
+    </row>
+    <row r="150" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C150" s="4"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="4"/>
+    </row>
+    <row r="151" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C151" s="4"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="4"/>
+    </row>
+    <row r="152" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B151" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B152" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B153" t="s">
+      <c r="C152" s="4"/>
+      <c r="D152" s="5"/>
+      <c r="E152" s="4"/>
+    </row>
+    <row r="153" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="5"/>
+      <c r="E153" s="4"/>
+    </row>
+    <row r="154" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C154" s="4"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="4"/>
+    </row>
+    <row r="155" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C155" s="4"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="4"/>
+    </row>
+    <row r="156" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C156" s="4"/>
+      <c r="D156" s="5"/>
+      <c r="E156" s="4"/>
+    </row>
+    <row r="157" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C157" s="4"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="4"/>
+    </row>
+    <row r="158" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B158" s="4" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B154" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B155" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B156" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B157" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B158" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B159" t="s">
+      <c r="C158" s="4"/>
+      <c r="D158" s="5"/>
+      <c r="E158" s="4"/>
+    </row>
+    <row r="159" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C159" s="4"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="4"/>
+    </row>
+    <row r="160" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B160" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C160" s="4"/>
+      <c r="D160" s="5"/>
+      <c r="E160" s="4"/>
+    </row>
+    <row r="161" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B161" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C161" s="4"/>
+      <c r="D161" s="5"/>
+      <c r="E161" s="4"/>
+    </row>
+    <row r="162" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="5"/>
+      <c r="E162" s="4"/>
+    </row>
+    <row r="163" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C163" s="4"/>
+      <c r="D163" s="5"/>
+      <c r="E163" s="4"/>
+    </row>
+    <row r="164" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="4" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B160" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B161" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B162" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B163" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B164" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B165" t="s">
+      <c r="C164" s="4"/>
+      <c r="D164" s="5"/>
+      <c r="E164" s="4"/>
+    </row>
+    <row r="165" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="4" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B166" t="s">
+      <c r="C165" s="4"/>
+      <c r="D165" s="5"/>
+      <c r="E165" s="4"/>
+    </row>
+    <row r="166" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="4" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B167" t="s">
+      <c r="C166" s="4"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="4"/>
+    </row>
+    <row r="167" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="4" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B168" t="s">
+      <c r="C167" s="4"/>
+      <c r="D167" s="5"/>
+      <c r="E167" s="4"/>
+    </row>
+    <row r="168" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B168" s="4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B169" t="s">
+      <c r="C168" s="4"/>
+      <c r="D168" s="5"/>
+      <c r="E168" s="4"/>
+    </row>
+    <row r="169" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C169" s="4"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="4"/>
+    </row>
+    <row r="170" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C170" s="4"/>
+      <c r="D170" s="5"/>
+      <c r="E170" s="4"/>
+    </row>
+    <row r="171" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B171" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C171" s="4"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="4"/>
+    </row>
+    <row r="172" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C172" s="4"/>
+      <c r="D172" s="5"/>
+      <c r="E172" s="4"/>
+    </row>
+    <row r="173" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B173" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C173" s="4"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="4"/>
+    </row>
+    <row r="174" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B174" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C174" s="4"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="4"/>
+    </row>
+    <row r="175" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B175" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C175" s="4"/>
+      <c r="D175" s="5"/>
+      <c r="E175" s="4"/>
+    </row>
+    <row r="176" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B176" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C176" s="4"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="4"/>
+    </row>
+    <row r="177" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B177" s="4" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B170" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B171" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B172" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B173" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B174" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B175" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B176" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B177" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B178" t="s">
+      <c r="C177" s="4"/>
+      <c r="D177" s="5"/>
+      <c r="E177" s="4"/>
+    </row>
+    <row r="178" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B178" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C178" s="4"/>
+      <c r="D178" s="5"/>
+      <c r="E178" s="4"/>
+    </row>
+    <row r="179" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B179" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C179" s="4"/>
+      <c r="D179" s="5"/>
+      <c r="E179" s="4"/>
+    </row>
+    <row r="180" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B180" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C180" s="4"/>
+      <c r="D180" s="5"/>
+      <c r="E180" s="4"/>
+    </row>
+    <row r="181" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B181" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C181" s="4"/>
+      <c r="D181" s="5"/>
+      <c r="E181" s="4"/>
+    </row>
+    <row r="182" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B182" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C182" s="4"/>
+      <c r="D182" s="5"/>
+      <c r="E182" s="4"/>
+    </row>
+    <row r="183" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B183" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C183" s="4"/>
+      <c r="D183" s="5"/>
+      <c r="E183" s="4"/>
+    </row>
+    <row r="184" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B184" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C184" s="4"/>
+      <c r="D184" s="5"/>
+      <c r="E184" s="4"/>
+    </row>
+    <row r="185" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B185" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B179" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B180" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B181" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B182" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B183" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B184" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B185" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B186" t="s">
+      <c r="C185" s="4"/>
+      <c r="D185" s="5"/>
+      <c r="E185" s="4"/>
+    </row>
+    <row r="186" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B186" s="4" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B187" t="s">
+      <c r="C186" s="4"/>
+      <c r="D186" s="5"/>
+      <c r="E186" s="4"/>
+    </row>
+    <row r="187" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B187" s="4" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B188" t="s">
+      <c r="C187" s="4"/>
+      <c r="D187" s="5"/>
+      <c r="E187" s="4"/>
+    </row>
+    <row r="188" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B188" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C188" s="4"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="4"/>
+    </row>
+    <row r="189" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B189" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C189" s="4"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="4"/>
+    </row>
+    <row r="190" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B190" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B189" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B190" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B191" t="s">
+      <c r="C190" s="4"/>
+      <c r="D190" s="5"/>
+      <c r="E190" s="4"/>
+    </row>
+    <row r="191" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B191" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C191" s="4"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="4"/>
+    </row>
+    <row r="192" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B192" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C192" s="4"/>
+      <c r="D192" s="5"/>
+      <c r="E192" s="4"/>
+    </row>
+    <row r="193" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B193" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C193" s="4"/>
+      <c r="D193" s="5"/>
+      <c r="E193" s="4"/>
+    </row>
+    <row r="194" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B194" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C194" s="4"/>
+      <c r="D194" s="5"/>
+      <c r="E194" s="4"/>
+    </row>
+    <row r="195" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B195" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C195" s="4"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="4"/>
+    </row>
+    <row r="196" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B196" s="4" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B192" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B193" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B194" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B195" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B196" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B197" t="s">
+      <c r="C196" s="4"/>
+      <c r="D196" s="5"/>
+      <c r="E196" s="4"/>
+    </row>
+    <row r="197" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B197" s="4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B198" t="s">
+      <c r="C197" s="4"/>
+      <c r="D197" s="5"/>
+      <c r="E197" s="4"/>
+    </row>
+    <row r="198" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B198" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C198" s="4"/>
+      <c r="D198" s="5"/>
+      <c r="E198" s="4"/>
+    </row>
+    <row r="199" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="4" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B199" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B200" t="s">
+      <c r="C199" s="4"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="4"/>
+    </row>
+    <row r="200" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B200" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C200" s="4"/>
+      <c r="D200" s="5"/>
+      <c r="E200" s="4"/>
+    </row>
+    <row r="201" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B201" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C201" s="4"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="4"/>
+    </row>
+    <row r="202" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="4" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B201" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B202" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B203" t="s">
+      <c r="C202" s="4"/>
+      <c r="D202" s="5"/>
+      <c r="E202" s="4"/>
+    </row>
+    <row r="203" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B203" s="4" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B204" t="s">
-        <v>208</v>
-      </c>
+      <c r="C203" s="4"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="4"/>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D204" s="1"/>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D205" s="1"/>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D206" s="1"/>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D207" s="1"/>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D208" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="32" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Control.xlsx
+++ b/Control.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526BABFF-BB27-4798-BE81-221A2BF88BC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3302B5-894B-42B6-AE80-012ACC8CAA4B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4380" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="210">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -652,6 +652,9 @@
   </si>
   <si>
     <t>Ricardo</t>
+  </si>
+  <si>
+    <t>No tiene consultas</t>
   </si>
 </sst>
 </file>
@@ -736,7 +739,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -758,6 +761,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bueno" xfId="1" builtinId="26"/>
@@ -1108,7 +1113,7 @@
       <c r="B2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="10"/>
       <c r="D2" s="5" t="s">
         <v>208</v>
       </c>
@@ -1120,40 +1125,50 @@
       <c r="B3" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="4" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="6" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="7" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3302B5-894B-42B6-AE80-012ACC8CAA4B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1971EBCA-091D-4D73-9C86-501008A2372E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4380" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
@@ -1175,7 +1175,7 @@
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="5"/>
       <c r="E8" s="7"/>
     </row>

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1971EBCA-091D-4D73-9C86-501008A2372E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EE8346-4789-4EC8-9DF3-D4FCA8A9BB78}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4380" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="211">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -655,6 +655,9 @@
   </si>
   <si>
     <t>No tiene consultas</t>
+  </si>
+  <si>
+    <t>No ejecuta consulta</t>
   </si>
 </sst>
 </file>
@@ -739,7 +742,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -763,6 +766,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bueno" xfId="1" builtinId="26"/>
@@ -1176,87 +1180,109 @@
         <v>2</v>
       </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E8" s="7"/>
     </row>
     <row r="9" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E9" s="7"/>
     </row>
     <row r="10" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="14" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="10"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="18" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EE8346-4789-4EC8-9DF3-D4FCA8A9BB78}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3722E00-718B-45CB-9DED-7A25E1FCEDA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4380" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1289,7 +1289,7 @@
       <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="4"/>
+      <c r="C19" s="10"/>
       <c r="D19" s="5"/>
       <c r="E19" s="7"/>
     </row>
@@ -1297,7 +1297,7 @@
       <c r="B20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="5"/>
       <c r="E20" s="7"/>
     </row>
@@ -1305,7 +1305,7 @@
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="10"/>
       <c r="D21" s="5"/>
       <c r="E21" s="7"/>
     </row>
@@ -1313,7 +1313,7 @@
       <c r="B22" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="10"/>
       <c r="D22" s="5"/>
       <c r="E22" s="7"/>
     </row>

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3722E00-718B-45CB-9DED-7A25E1FCEDA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F96190D-6215-480E-B7E9-15B9F1A20041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4380" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
+    <workbookView xWindow="1125" yWindow="1245" windowWidth="25860" windowHeight="11295" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="213">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -658,13 +658,19 @@
   </si>
   <si>
     <t>No ejecuta consulta</t>
+  </si>
+  <si>
+    <t>Arturo</t>
+  </si>
+  <si>
+    <t>Indice ya quedo usando conn. Pool</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +695,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -742,7 +755,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -767,6 +780,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bueno" xfId="1" builtinId="26"/>
@@ -787,9 +803,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -827,7 +843,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -933,7 +949,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1075,7 +1091,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1617,9 +1633,13 @@
       <c r="B60" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="7"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="61" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F96190D-6215-480E-B7E9-15B9F1A20041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEE646A-C9E0-4FDA-A26B-CB74F00B7917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="1245" windowWidth="25860" windowHeight="11295" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="220">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -664,6 +664,27 @@
   </si>
   <si>
     <t>Indice ya quedo usando conn. Pool</t>
+  </si>
+  <si>
+    <t>obtmza_acu_rec.jsp (2 matches)</t>
+  </si>
+  <si>
+    <t>obtmza_acu.jsp (2 matches)</t>
+  </si>
+  <si>
+    <t>obtmza.jsp (2 matches)</t>
+  </si>
+  <si>
+    <t>obtregsap.jsp (2 matches)</t>
+  </si>
+  <si>
+    <t>real.jsp (4 matches)</t>
+  </si>
+  <si>
+    <t>regresa_varios.jsp (2 matches)</t>
+  </si>
+  <si>
+    <t>DESTINO</t>
   </si>
 </sst>
 </file>
@@ -1098,1710 +1119,2981 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CFB12C-C000-4D62-A088-E6A986C2EDDD}">
-  <dimension ref="B1:G208"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B59B5D-84E1-4758-8A86-CC0AE209F4CF}">
+  <dimension ref="C2:H547"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="42.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+    <row r="2" spans="3:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G2" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="3:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C72" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+    </row>
+    <row r="73" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C73" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+    </row>
+    <row r="79" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C79" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+    </row>
+    <row r="80" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C80" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+    </row>
+    <row r="82" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C82" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C83" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+    </row>
+    <row r="84" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C84" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C85" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C86" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C87" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C88" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C89" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+    </row>
+    <row r="91" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+    </row>
+    <row r="92" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+    </row>
+    <row r="93" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+    </row>
+    <row r="94" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C94" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+    </row>
+    <row r="95" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+    </row>
+    <row r="96" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+    </row>
+    <row r="97" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+    </row>
+    <row r="98" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+    </row>
+    <row r="99" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+    </row>
+    <row r="100" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C100" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+    </row>
+    <row r="101" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C101" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+    </row>
+    <row r="102" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+    </row>
+    <row r="103" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+    </row>
+    <row r="104" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C104" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+    </row>
+    <row r="105" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+    </row>
+    <row r="106" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C106" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+    </row>
+    <row r="107" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+    </row>
+    <row r="108" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+    </row>
+    <row r="109" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+    </row>
+    <row r="110" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+    </row>
+    <row r="111" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+    </row>
+    <row r="112" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C112" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+    </row>
+    <row r="113" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C113" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+    </row>
+    <row r="114" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C114" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+    </row>
+    <row r="115" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+    </row>
+    <row r="116" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C116" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+    </row>
+    <row r="117" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C117" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+    </row>
+    <row r="118" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C118" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+    </row>
+    <row r="119" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C119" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+    </row>
+    <row r="120" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C120" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+    </row>
+    <row r="121" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C121" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+    </row>
+    <row r="122" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C122" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+    </row>
+    <row r="123" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C123" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+    </row>
+    <row r="124" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C124" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+    </row>
+    <row r="125" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C125" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+    </row>
+    <row r="126" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C126" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+    </row>
+    <row r="127" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="4"/>
+    </row>
+    <row r="128" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C128" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
+    </row>
+    <row r="129" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C129" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+    </row>
+    <row r="130" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C130" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="4"/>
+    </row>
+    <row r="131" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C131" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="4"/>
+    </row>
+    <row r="132" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C132" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4"/>
+      <c r="G132" s="4"/>
+    </row>
+    <row r="133" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C133" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+      <c r="G133" s="4"/>
+    </row>
+    <row r="134" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C134" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D134" s="10"/>
+      <c r="E134" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F134" s="4"/>
+      <c r="G134" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C344" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E344" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F344" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G344" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H344" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="345" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C345" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="5" t="s">
+      <c r="D345" s="10"/>
+      <c r="E345" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="F345" s="7"/>
+      <c r="G345" s="6"/>
+      <c r="H345" s="2"/>
+    </row>
+    <row r="346" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C346" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="7" t="s">
+      <c r="D346" s="9"/>
+      <c r="E346" s="5"/>
+      <c r="F346" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+    <row r="347" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C347" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="5" t="s">
+      <c r="D347" s="10"/>
+      <c r="E347" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="F347" s="7"/>
+    </row>
+    <row r="348" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C348" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="7" t="s">
+      <c r="D348" s="10"/>
+      <c r="E348" s="5"/>
+      <c r="F348" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+    <row r="349" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C349" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="7" t="s">
+      <c r="D349" s="9"/>
+      <c r="E349" s="5"/>
+      <c r="F349" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="350" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C350" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="5" t="s">
+      <c r="D350" s="10"/>
+      <c r="E350" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="F350" s="7"/>
+    </row>
+    <row r="351" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C351" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="5" t="s">
+      <c r="D351" s="10"/>
+      <c r="E351" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="F351" s="7"/>
+    </row>
+    <row r="352" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C352" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="5" t="s">
+      <c r="D352" s="11"/>
+      <c r="E352" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="F352" s="7"/>
+    </row>
+    <row r="353" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C353" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="5" t="s">
+      <c r="D353" s="10"/>
+      <c r="E353" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+      <c r="F353" s="7"/>
+    </row>
+    <row r="354" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C354" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="5" t="s">
+      <c r="D354" s="10"/>
+      <c r="E354" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+      <c r="F354" s="7"/>
+    </row>
+    <row r="355" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C355" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="5" t="s">
+      <c r="D355" s="10"/>
+      <c r="E355" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+      <c r="F355" s="7"/>
+    </row>
+    <row r="356" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C356" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="7" t="s">
+      <c r="D356" s="10"/>
+      <c r="E356" s="5"/>
+      <c r="F356" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="357" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C357" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="5" t="s">
+      <c r="D357" s="10"/>
+      <c r="E357" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
+      <c r="F357" s="7"/>
+    </row>
+    <row r="358" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C358" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="5" t="s">
+      <c r="D358" s="10"/>
+      <c r="E358" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="2:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
+      <c r="F358" s="7"/>
+    </row>
+    <row r="359" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C359" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="5" t="s">
+      <c r="D359" s="10"/>
+      <c r="E359" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+      <c r="F359" s="7"/>
+    </row>
+    <row r="360" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C360" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="7" t="s">
+      <c r="D360" s="10"/>
+      <c r="E360" s="5"/>
+      <c r="F360" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
+    <row r="361" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C361" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="5" t="s">
+      <c r="D361" s="10"/>
+      <c r="E361" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+      <c r="F361" s="7"/>
+    </row>
+    <row r="362" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C362" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
+      <c r="D362" s="10"/>
+      <c r="E362" s="5"/>
+      <c r="F362" s="7"/>
+    </row>
+    <row r="363" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C363" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
+      <c r="D363" s="10"/>
+      <c r="E363" s="5"/>
+      <c r="F363" s="7"/>
+    </row>
+    <row r="364" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C364" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
+      <c r="D364" s="10"/>
+      <c r="E364" s="5"/>
+      <c r="F364" s="7"/>
+    </row>
+    <row r="365" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C365" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+      <c r="D365" s="10"/>
+      <c r="E365" s="5"/>
+      <c r="F365" s="7"/>
+    </row>
+    <row r="366" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C366" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
+      <c r="D366" s="10"/>
+      <c r="E366" s="5"/>
+      <c r="F366" s="7"/>
+    </row>
+    <row r="367" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C367" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
+      <c r="D367" s="10"/>
+      <c r="E367" s="5"/>
+      <c r="F367" s="7"/>
+    </row>
+    <row r="368" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C368" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
+      <c r="D368" s="10"/>
+      <c r="E368" s="5"/>
+      <c r="F368" s="7"/>
+    </row>
+    <row r="369" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C369" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
+      <c r="D369" s="4"/>
+      <c r="E369" s="5"/>
+      <c r="F369" s="7"/>
+    </row>
+    <row r="370" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C370" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
+      <c r="D370" s="4"/>
+      <c r="E370" s="5"/>
+      <c r="F370" s="7"/>
+    </row>
+    <row r="371" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C371" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
+      <c r="D371" s="4"/>
+      <c r="E371" s="5"/>
+      <c r="F371" s="7"/>
+    </row>
+    <row r="372" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C372" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
+      <c r="D372" s="4"/>
+      <c r="E372" s="5"/>
+      <c r="F372" s="7"/>
+    </row>
+    <row r="373" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C373" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
+      <c r="D373" s="4"/>
+      <c r="E373" s="5"/>
+      <c r="F373" s="7"/>
+    </row>
+    <row r="374" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C374" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="32" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="4" t="s">
+      <c r="D374" s="4"/>
+      <c r="E374" s="5"/>
+      <c r="F374" s="7"/>
+    </row>
+    <row r="375" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C375" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="7"/>
-    </row>
-    <row r="33" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
+      <c r="D375" s="4"/>
+      <c r="E375" s="5"/>
+      <c r="F375" s="7"/>
+    </row>
+    <row r="376" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C376" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="7"/>
-    </row>
-    <row r="34" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
+      <c r="D376" s="4"/>
+      <c r="E376" s="5"/>
+      <c r="F376" s="7"/>
+    </row>
+    <row r="377" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C377" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="4" t="s">
+      <c r="D377" s="4"/>
+      <c r="E377" s="5"/>
+      <c r="F377" s="7"/>
+    </row>
+    <row r="378" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C378" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="7"/>
-    </row>
-    <row r="36" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="4" t="s">
+      <c r="D378" s="4"/>
+      <c r="E378" s="5"/>
+      <c r="F378" s="7"/>
+    </row>
+    <row r="379" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C379" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="7"/>
-    </row>
-    <row r="37" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="4" t="s">
+      <c r="D379" s="4"/>
+      <c r="E379" s="5"/>
+      <c r="F379" s="7"/>
+    </row>
+    <row r="380" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C380" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="4" t="s">
+      <c r="D380" s="4"/>
+      <c r="E380" s="5"/>
+      <c r="F380" s="7"/>
+    </row>
+    <row r="381" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C381" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="7"/>
-    </row>
-    <row r="39" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
+      <c r="D381" s="4"/>
+      <c r="E381" s="5"/>
+      <c r="F381" s="7"/>
+    </row>
+    <row r="382" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C382" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="7"/>
-    </row>
-    <row r="40" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="4" t="s">
+      <c r="D382" s="4"/>
+      <c r="E382" s="5"/>
+      <c r="F382" s="7"/>
+    </row>
+    <row r="383" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C383" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="4" t="s">
+      <c r="D383" s="4"/>
+      <c r="E383" s="5"/>
+      <c r="F383" s="7"/>
+    </row>
+    <row r="384" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C384" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="4" t="s">
+      <c r="D384" s="4"/>
+      <c r="E384" s="5"/>
+      <c r="F384" s="7"/>
+    </row>
+    <row r="385" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C385" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="7"/>
-    </row>
-    <row r="43" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="4" t="s">
+      <c r="D385" s="4"/>
+      <c r="E385" s="5"/>
+      <c r="F385" s="7"/>
+    </row>
+    <row r="386" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C386" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="4" t="s">
+      <c r="D386" s="4"/>
+      <c r="E386" s="5"/>
+      <c r="F386" s="7"/>
+    </row>
+    <row r="387" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C387" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="4" t="s">
+      <c r="D387" s="4"/>
+      <c r="E387" s="5"/>
+      <c r="F387" s="7"/>
+    </row>
+    <row r="388" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C388" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
+      <c r="D388" s="4"/>
+      <c r="E388" s="5"/>
+      <c r="F388" s="7"/>
+    </row>
+    <row r="389" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C389" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="4" t="s">
+      <c r="D389" s="4"/>
+      <c r="E389" s="5"/>
+      <c r="F389" s="7"/>
+    </row>
+    <row r="390" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C390" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="7"/>
-    </row>
-    <row r="48" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="4" t="s">
+      <c r="D390" s="4"/>
+      <c r="E390" s="5"/>
+      <c r="F390" s="7"/>
+    </row>
+    <row r="391" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C391" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="4" t="s">
+      <c r="D391" s="4"/>
+      <c r="E391" s="5"/>
+      <c r="F391" s="7"/>
+    </row>
+    <row r="392" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C392" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="4" t="s">
+      <c r="D392" s="4"/>
+      <c r="E392" s="5"/>
+      <c r="F392" s="7"/>
+    </row>
+    <row r="393" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C393" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="7"/>
-    </row>
-    <row r="51" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="4" t="s">
+      <c r="D393" s="4"/>
+      <c r="E393" s="5"/>
+      <c r="F393" s="7"/>
+    </row>
+    <row r="394" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C394" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="7"/>
-    </row>
-    <row r="52" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="4" t="s">
+      <c r="D394" s="4"/>
+      <c r="E394" s="5"/>
+      <c r="F394" s="7"/>
+    </row>
+    <row r="395" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C395" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="7"/>
-    </row>
-    <row r="53" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="4" t="s">
+      <c r="D395" s="4"/>
+      <c r="E395" s="5"/>
+      <c r="F395" s="7"/>
+    </row>
+    <row r="396" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C396" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="7"/>
-    </row>
-    <row r="54" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
+      <c r="D396" s="4"/>
+      <c r="E396" s="5"/>
+      <c r="F396" s="7"/>
+    </row>
+    <row r="397" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C397" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="7"/>
-    </row>
-    <row r="55" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="4" t="s">
+      <c r="D397" s="4"/>
+      <c r="E397" s="5"/>
+      <c r="F397" s="7"/>
+    </row>
+    <row r="398" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C398" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="7"/>
-    </row>
-    <row r="56" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="4" t="s">
+      <c r="D398" s="4"/>
+      <c r="E398" s="5"/>
+      <c r="F398" s="7"/>
+    </row>
+    <row r="399" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C399" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="7"/>
-    </row>
-    <row r="57" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="8" t="s">
+      <c r="D399" s="4"/>
+      <c r="E399" s="5"/>
+      <c r="F399" s="7"/>
+    </row>
+    <row r="400" spans="3:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="C400" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="7"/>
-    </row>
-    <row r="58" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="4" t="s">
+      <c r="D400" s="4"/>
+      <c r="E400" s="5"/>
+      <c r="F400" s="7"/>
+    </row>
+    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C401" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="7"/>
-    </row>
-    <row r="59" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="4" t="s">
+      <c r="D401" s="4"/>
+      <c r="E401" s="5"/>
+      <c r="F401" s="7"/>
+    </row>
+    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C402" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="7"/>
-    </row>
-    <row r="60" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="4" t="s">
+      <c r="D402" s="4"/>
+      <c r="E402" s="5"/>
+      <c r="F402" s="7"/>
+    </row>
+    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C403" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="5" t="s">
+      <c r="D403" s="10"/>
+      <c r="E403" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="F403" s="12" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="61" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="4" t="s">
+    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C404" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="7"/>
-    </row>
-    <row r="62" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="4" t="s">
+      <c r="D404" s="4"/>
+      <c r="E404" s="5"/>
+      <c r="F404" s="7"/>
+    </row>
+    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C405" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="7"/>
-    </row>
-    <row r="63" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="4" t="s">
+      <c r="D405" s="4"/>
+      <c r="E405" s="5"/>
+      <c r="F405" s="7"/>
+    </row>
+    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C406" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="7"/>
-    </row>
-    <row r="64" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
+      <c r="D406" s="4"/>
+      <c r="E406" s="5"/>
+      <c r="F406" s="7"/>
+    </row>
+    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C407" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="7"/>
-    </row>
-    <row r="65" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="4" t="s">
+      <c r="D407" s="4"/>
+      <c r="E407" s="5"/>
+      <c r="F407" s="7"/>
+    </row>
+    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C408" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="7"/>
-    </row>
-    <row r="66" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="4" t="s">
+      <c r="D408" s="4"/>
+      <c r="E408" s="5"/>
+      <c r="F408" s="7"/>
+    </row>
+    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C409" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="7"/>
-    </row>
-    <row r="67" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="4" t="s">
+      <c r="D409" s="4"/>
+      <c r="E409" s="5"/>
+      <c r="F409" s="7"/>
+    </row>
+    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C410" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="7"/>
-    </row>
-    <row r="68" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="4" t="s">
+      <c r="D410" s="4"/>
+      <c r="E410" s="5"/>
+      <c r="F410" s="7"/>
+    </row>
+    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C411" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="7"/>
-    </row>
-    <row r="69" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="4" t="s">
+      <c r="D411" s="4"/>
+      <c r="E411" s="5"/>
+      <c r="F411" s="7"/>
+    </row>
+    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C412" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C69" s="4"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="7"/>
-    </row>
-    <row r="70" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="4" t="s">
+      <c r="D412" s="4"/>
+      <c r="E412" s="5"/>
+      <c r="F412" s="7"/>
+    </row>
+    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C413" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C70" s="4"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="7"/>
-    </row>
-    <row r="71" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="4" t="s">
+      <c r="D413" s="4"/>
+      <c r="E413" s="5"/>
+      <c r="F413" s="7"/>
+    </row>
+    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C414" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="7"/>
-    </row>
-    <row r="72" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="4" t="s">
+      <c r="D414" s="4"/>
+      <c r="E414" s="5"/>
+      <c r="F414" s="7"/>
+    </row>
+    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C415" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="7"/>
-    </row>
-    <row r="73" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="4" t="s">
+      <c r="D415" s="4"/>
+      <c r="E415" s="5"/>
+      <c r="F415" s="7"/>
+    </row>
+    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C416" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C73" s="4"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="7"/>
-    </row>
-    <row r="74" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="4" t="s">
+      <c r="D416" s="4"/>
+      <c r="E416" s="5"/>
+      <c r="F416" s="7"/>
+    </row>
+    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C417" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="7"/>
-    </row>
-    <row r="75" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="4" t="s">
+      <c r="D417" s="4"/>
+      <c r="E417" s="5"/>
+      <c r="F417" s="7"/>
+    </row>
+    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C418" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C75" s="4"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="7"/>
-    </row>
-    <row r="76" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="4" t="s">
+      <c r="D418" s="4"/>
+      <c r="E418" s="5"/>
+      <c r="F418" s="7"/>
+    </row>
+    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C419" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="7"/>
-    </row>
-    <row r="77" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="4" t="s">
+      <c r="D419" s="4"/>
+      <c r="E419" s="5"/>
+      <c r="F419" s="7"/>
+    </row>
+    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C420" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="7"/>
-    </row>
-    <row r="78" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="4" t="s">
+      <c r="D420" s="4"/>
+      <c r="E420" s="5"/>
+      <c r="F420" s="7"/>
+    </row>
+    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C421" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="7"/>
-    </row>
-    <row r="79" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="4" t="s">
+      <c r="D421" s="4"/>
+      <c r="E421" s="5"/>
+      <c r="F421" s="7"/>
+    </row>
+    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C422" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="7"/>
-    </row>
-    <row r="80" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="4" t="s">
+      <c r="D422" s="4"/>
+      <c r="E422" s="5"/>
+      <c r="F422" s="7"/>
+    </row>
+    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C423" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="7"/>
-    </row>
-    <row r="81" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="4" t="s">
+      <c r="D423" s="4"/>
+      <c r="E423" s="5"/>
+      <c r="F423" s="7"/>
+    </row>
+    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C424" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="7"/>
-    </row>
-    <row r="82" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="4" t="s">
+      <c r="D424" s="4"/>
+      <c r="E424" s="5"/>
+      <c r="F424" s="7"/>
+    </row>
+    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C425" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="7"/>
-    </row>
-    <row r="83" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="4" t="s">
+      <c r="D425" s="4"/>
+      <c r="E425" s="5"/>
+      <c r="F425" s="7"/>
+    </row>
+    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C426" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C83" s="4"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="7"/>
-    </row>
-    <row r="84" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="4" t="s">
+      <c r="D426" s="4"/>
+      <c r="E426" s="5"/>
+      <c r="F426" s="7"/>
+    </row>
+    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C427" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C84" s="4"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="7"/>
-    </row>
-    <row r="85" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="4" t="s">
+      <c r="D427" s="4"/>
+      <c r="E427" s="5"/>
+      <c r="F427" s="7"/>
+    </row>
+    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C428" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C85" s="4"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="7"/>
-    </row>
-    <row r="86" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="4" t="s">
+      <c r="D428" s="4"/>
+      <c r="E428" s="5"/>
+      <c r="F428" s="7"/>
+    </row>
+    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C429" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C86" s="4"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="7"/>
-    </row>
-    <row r="87" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="4" t="s">
+      <c r="D429" s="4"/>
+      <c r="E429" s="5"/>
+      <c r="F429" s="7"/>
+    </row>
+    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C430" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="7"/>
-    </row>
-    <row r="88" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="4" t="s">
+      <c r="D430" s="4"/>
+      <c r="E430" s="5"/>
+      <c r="F430" s="7"/>
+    </row>
+    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C431" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C88" s="4"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="7"/>
-    </row>
-    <row r="89" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="4" t="s">
+      <c r="D431" s="4"/>
+      <c r="E431" s="5"/>
+      <c r="F431" s="7"/>
+    </row>
+    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C432" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="7"/>
-    </row>
-    <row r="90" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="4" t="s">
+      <c r="D432" s="4"/>
+      <c r="E432" s="5"/>
+      <c r="F432" s="7"/>
+    </row>
+    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C433" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C90" s="4"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="7"/>
-    </row>
-    <row r="91" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="4" t="s">
+      <c r="D433" s="4"/>
+      <c r="E433" s="5"/>
+      <c r="F433" s="7"/>
+    </row>
+    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C434" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="7"/>
-    </row>
-    <row r="92" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="4" t="s">
+      <c r="D434" s="4"/>
+      <c r="E434" s="5"/>
+      <c r="F434" s="7"/>
+    </row>
+    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C435" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C92" s="4"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="7"/>
-    </row>
-    <row r="93" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="4" t="s">
+      <c r="D435" s="4"/>
+      <c r="E435" s="5"/>
+      <c r="F435" s="7"/>
+    </row>
+    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C436" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C93" s="4"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="7"/>
-    </row>
-    <row r="94" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="4" t="s">
+      <c r="D436" s="4"/>
+      <c r="E436" s="5"/>
+      <c r="F436" s="7"/>
+    </row>
+    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C437" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C94" s="4"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="7"/>
-    </row>
-    <row r="95" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="4" t="s">
+      <c r="D437" s="4"/>
+      <c r="E437" s="5"/>
+      <c r="F437" s="7"/>
+    </row>
+    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C438" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C95" s="4"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="7"/>
-    </row>
-    <row r="96" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="4" t="s">
+      <c r="D438" s="4"/>
+      <c r="E438" s="5"/>
+      <c r="F438" s="7"/>
+    </row>
+    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C439" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C96" s="4"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="7"/>
-    </row>
-    <row r="97" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="4" t="s">
+      <c r="D439" s="4"/>
+      <c r="E439" s="5"/>
+      <c r="F439" s="7"/>
+    </row>
+    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C440" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C97" s="4"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="7"/>
-    </row>
-    <row r="98" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="4" t="s">
+      <c r="D440" s="4"/>
+      <c r="E440" s="5"/>
+      <c r="F440" s="7"/>
+    </row>
+    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C441" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C98" s="4"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="7"/>
-    </row>
-    <row r="99" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="4" t="s">
+      <c r="D441" s="4"/>
+      <c r="E441" s="5"/>
+      <c r="F441" s="7"/>
+    </row>
+    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C442" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C99" s="4"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="7"/>
-    </row>
-    <row r="100" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="4" t="s">
+      <c r="D442" s="4"/>
+      <c r="E442" s="5"/>
+      <c r="F442" s="7"/>
+    </row>
+    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C443" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="7"/>
-    </row>
-    <row r="101" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="4" t="s">
+      <c r="D443" s="4"/>
+      <c r="E443" s="5"/>
+      <c r="F443" s="7"/>
+    </row>
+    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C444" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C101" s="4"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="7"/>
-    </row>
-    <row r="102" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="4" t="s">
+      <c r="D444" s="4"/>
+      <c r="E444" s="5"/>
+      <c r="F444" s="7"/>
+    </row>
+    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C445" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="7"/>
-    </row>
-    <row r="103" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="4" t="s">
+      <c r="D445" s="4"/>
+      <c r="E445" s="5"/>
+      <c r="F445" s="7"/>
+    </row>
+    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C446" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C103" s="4"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="7"/>
-    </row>
-    <row r="104" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="4" t="s">
+      <c r="D446" s="4"/>
+      <c r="E446" s="5"/>
+      <c r="F446" s="7"/>
+    </row>
+    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C447" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C104" s="4"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="7"/>
-    </row>
-    <row r="105" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="4" t="s">
+      <c r="D447" s="4"/>
+      <c r="E447" s="5"/>
+      <c r="F447" s="7"/>
+    </row>
+    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C448" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C105" s="4"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="7"/>
-    </row>
-    <row r="106" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="4" t="s">
+      <c r="D448" s="4"/>
+      <c r="E448" s="5"/>
+      <c r="F448" s="7"/>
+    </row>
+    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C449" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="7"/>
-    </row>
-    <row r="107" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="4" t="s">
+      <c r="D449" s="4"/>
+      <c r="E449" s="5"/>
+      <c r="F449" s="7"/>
+    </row>
+    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C450" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C107" s="4"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="7"/>
-    </row>
-    <row r="108" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="4" t="s">
+      <c r="D450" s="4"/>
+      <c r="E450" s="5"/>
+      <c r="F450" s="7"/>
+    </row>
+    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C451" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="7"/>
-    </row>
-    <row r="109" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="4" t="s">
+      <c r="D451" s="4"/>
+      <c r="E451" s="5"/>
+      <c r="F451" s="7"/>
+    </row>
+    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C452" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C109" s="4"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="7"/>
-    </row>
-    <row r="110" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="4" t="s">
+      <c r="D452" s="4"/>
+      <c r="E452" s="5"/>
+      <c r="F452" s="7"/>
+    </row>
+    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C453" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="7"/>
-    </row>
-    <row r="111" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="4" t="s">
+      <c r="D453" s="4"/>
+      <c r="E453" s="5"/>
+      <c r="F453" s="7"/>
+    </row>
+    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C454" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="7"/>
-    </row>
-    <row r="112" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="4" t="s">
+      <c r="D454" s="4"/>
+      <c r="E454" s="5"/>
+      <c r="F454" s="7"/>
+    </row>
+    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C455" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="7"/>
-    </row>
-    <row r="113" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="4" t="s">
+      <c r="D455" s="4"/>
+      <c r="E455" s="5"/>
+      <c r="F455" s="7"/>
+    </row>
+    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C456" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="7"/>
-    </row>
-    <row r="114" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="4" t="s">
+      <c r="D456" s="4"/>
+      <c r="E456" s="5"/>
+      <c r="F456" s="7"/>
+    </row>
+    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C457" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="7"/>
-    </row>
-    <row r="115" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="4" t="s">
+      <c r="D457" s="4"/>
+      <c r="E457" s="5"/>
+      <c r="F457" s="7"/>
+    </row>
+    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C458" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C115" s="4"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="7"/>
-    </row>
-    <row r="116" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="4" t="s">
+      <c r="D458" s="4"/>
+      <c r="E458" s="5"/>
+      <c r="F458" s="7"/>
+    </row>
+    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C459" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C116" s="4"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="7"/>
-    </row>
-    <row r="117" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="4" t="s">
+      <c r="D459" s="4"/>
+      <c r="E459" s="5"/>
+      <c r="F459" s="7"/>
+    </row>
+    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C460" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C117" s="4"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="7"/>
-    </row>
-    <row r="118" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="4" t="s">
+      <c r="D460" s="4"/>
+      <c r="E460" s="5"/>
+      <c r="F460" s="7"/>
+    </row>
+    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C461" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C118" s="4"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="7"/>
-    </row>
-    <row r="119" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="4" t="s">
+      <c r="D461" s="4"/>
+      <c r="E461" s="5"/>
+      <c r="F461" s="7"/>
+    </row>
+    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C462" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C119" s="4"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="7"/>
-    </row>
-    <row r="120" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="4" t="s">
+      <c r="D462" s="4"/>
+      <c r="E462" s="5"/>
+      <c r="F462" s="7"/>
+    </row>
+    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C463" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C120" s="4"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="7"/>
-    </row>
-    <row r="121" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="4" t="s">
+      <c r="D463" s="4"/>
+      <c r="E463" s="5"/>
+      <c r="F463" s="7"/>
+    </row>
+    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C464" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C121" s="4"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="7"/>
-    </row>
-    <row r="122" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="4" t="s">
+      <c r="D464" s="4"/>
+      <c r="E464" s="5"/>
+      <c r="F464" s="7"/>
+    </row>
+    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C465" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C122" s="4"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="7"/>
-    </row>
-    <row r="123" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="4" t="s">
+      <c r="D465" s="4"/>
+      <c r="E465" s="5"/>
+      <c r="F465" s="7"/>
+    </row>
+    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C466" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C123" s="4"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="7"/>
-    </row>
-    <row r="124" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="4" t="s">
+      <c r="D466" s="4"/>
+      <c r="E466" s="5"/>
+      <c r="F466" s="7"/>
+    </row>
+    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C467" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C124" s="4"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="7"/>
-    </row>
-    <row r="125" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="4" t="s">
+      <c r="D467" s="4"/>
+      <c r="E467" s="5"/>
+      <c r="F467" s="7"/>
+    </row>
+    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C468" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C125" s="4"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="7"/>
-    </row>
-    <row r="126" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="4" t="s">
+      <c r="D468" s="4"/>
+      <c r="E468" s="5"/>
+      <c r="F468" s="7"/>
+    </row>
+    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C469" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C126" s="4"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="7"/>
-    </row>
-    <row r="127" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="4" t="s">
+      <c r="D469" s="4"/>
+      <c r="E469" s="5"/>
+      <c r="F469" s="7"/>
+    </row>
+    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C470" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C127" s="4"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="7"/>
-    </row>
-    <row r="128" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="4" t="s">
+      <c r="D470" s="4"/>
+      <c r="E470" s="5"/>
+      <c r="F470" s="7"/>
+    </row>
+    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C471" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C128" s="4"/>
-      <c r="D128" s="5"/>
-      <c r="E128" s="7"/>
-    </row>
-    <row r="129" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="4" t="s">
+      <c r="D471" s="4"/>
+      <c r="E471" s="5"/>
+      <c r="F471" s="7"/>
+    </row>
+    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C472" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C129" s="4"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="4"/>
-    </row>
-    <row r="130" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="4" t="s">
+      <c r="D472" s="4"/>
+      <c r="E472" s="5"/>
+      <c r="F472" s="4"/>
+    </row>
+    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C473" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C130" s="4"/>
-      <c r="D130" s="5"/>
-      <c r="E130" s="4"/>
-    </row>
-    <row r="131" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="4" t="s">
+      <c r="D473" s="4"/>
+      <c r="E473" s="5"/>
+      <c r="F473" s="4"/>
+    </row>
+    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C474" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C131" s="4"/>
-      <c r="D131" s="5"/>
-      <c r="E131" s="4"/>
-    </row>
-    <row r="132" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="4" t="s">
+      <c r="D474" s="4"/>
+      <c r="E474" s="5"/>
+      <c r="F474" s="4"/>
+    </row>
+    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C475" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C132" s="4"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="4"/>
-    </row>
-    <row r="133" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="4" t="s">
+      <c r="D475" s="4"/>
+      <c r="E475" s="5"/>
+      <c r="F475" s="4"/>
+    </row>
+    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C476" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C133" s="4"/>
-      <c r="D133" s="5"/>
-      <c r="E133" s="4"/>
-    </row>
-    <row r="134" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="4" t="s">
+      <c r="D476" s="4"/>
+      <c r="E476" s="5"/>
+      <c r="F476" s="4"/>
+    </row>
+    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C477" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C134" s="4"/>
-      <c r="D134" s="5"/>
-      <c r="E134" s="4"/>
-    </row>
-    <row r="135" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="4" t="s">
+      <c r="D477" s="4"/>
+      <c r="E477" s="5"/>
+      <c r="F477" s="4"/>
+    </row>
+    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C478" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C135" s="4"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="4"/>
-    </row>
-    <row r="136" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="4" t="s">
+      <c r="D478" s="4"/>
+      <c r="E478" s="5"/>
+      <c r="F478" s="4"/>
+    </row>
+    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C479" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C136" s="4"/>
-      <c r="D136" s="5"/>
-      <c r="E136" s="4"/>
-    </row>
-    <row r="137" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="4" t="s">
+      <c r="D479" s="4"/>
+      <c r="E479" s="5"/>
+      <c r="F479" s="4"/>
+    </row>
+    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C480" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C137" s="4"/>
-      <c r="D137" s="5"/>
-      <c r="E137" s="4"/>
-    </row>
-    <row r="138" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="4" t="s">
+      <c r="D480" s="4"/>
+      <c r="E480" s="5"/>
+      <c r="F480" s="4"/>
+    </row>
+    <row r="481" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C481" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C138" s="4"/>
-      <c r="D138" s="5"/>
-      <c r="E138" s="4"/>
-    </row>
-    <row r="139" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="4" t="s">
+      <c r="D481" s="4"/>
+      <c r="E481" s="5"/>
+      <c r="F481" s="4"/>
+    </row>
+    <row r="482" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C482" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C139" s="4"/>
-      <c r="D139" s="5"/>
-      <c r="E139" s="4"/>
-    </row>
-    <row r="140" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="4" t="s">
+      <c r="D482" s="4"/>
+      <c r="E482" s="5"/>
+      <c r="F482" s="4"/>
+    </row>
+    <row r="483" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C483" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C140" s="4"/>
-      <c r="D140" s="5"/>
-      <c r="E140" s="4"/>
-    </row>
-    <row r="141" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="4" t="s">
+      <c r="D483" s="4"/>
+      <c r="E483" s="5"/>
+      <c r="F483" s="4"/>
+    </row>
+    <row r="484" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C484" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C141" s="4"/>
-      <c r="D141" s="5"/>
-      <c r="E141" s="4"/>
-    </row>
-    <row r="142" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="4" t="s">
+      <c r="D484" s="4"/>
+      <c r="E484" s="5"/>
+      <c r="F484" s="4"/>
+    </row>
+    <row r="485" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C485" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C142" s="4"/>
-      <c r="D142" s="5"/>
-      <c r="E142" s="4"/>
-    </row>
-    <row r="143" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="4" t="s">
+      <c r="D485" s="4"/>
+      <c r="E485" s="5"/>
+      <c r="F485" s="4"/>
+    </row>
+    <row r="486" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C486" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C143" s="4"/>
-      <c r="D143" s="5"/>
-      <c r="E143" s="4"/>
-    </row>
-    <row r="144" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="4" t="s">
+      <c r="D486" s="4"/>
+      <c r="E486" s="5"/>
+      <c r="F486" s="4"/>
+    </row>
+    <row r="487" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C487" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C144" s="4"/>
-      <c r="D144" s="5"/>
-      <c r="E144" s="4"/>
-    </row>
-    <row r="145" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="4" t="s">
+      <c r="D487" s="4"/>
+      <c r="E487" s="5"/>
+      <c r="F487" s="4"/>
+    </row>
+    <row r="488" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C488" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C145" s="4"/>
-      <c r="D145" s="5"/>
-      <c r="E145" s="4"/>
-    </row>
-    <row r="146" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="4" t="s">
+      <c r="D488" s="4"/>
+      <c r="E488" s="5"/>
+      <c r="F488" s="4"/>
+    </row>
+    <row r="489" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C489" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C146" s="4"/>
-      <c r="D146" s="5"/>
-      <c r="E146" s="4"/>
-    </row>
-    <row r="147" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="4" t="s">
+      <c r="D489" s="4"/>
+      <c r="E489" s="5"/>
+      <c r="F489" s="4"/>
+    </row>
+    <row r="490" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C490" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C147" s="4"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="4"/>
-    </row>
-    <row r="148" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="4" t="s">
+      <c r="D490" s="4"/>
+      <c r="E490" s="5"/>
+      <c r="F490" s="4"/>
+    </row>
+    <row r="491" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C491" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C148" s="4"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="4"/>
-    </row>
-    <row r="149" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="4" t="s">
+      <c r="D491" s="4"/>
+      <c r="E491" s="5"/>
+      <c r="F491" s="4"/>
+    </row>
+    <row r="492" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C492" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C149" s="4"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="4"/>
-    </row>
-    <row r="150" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="4" t="s">
+      <c r="D492" s="4"/>
+      <c r="E492" s="5"/>
+      <c r="F492" s="4"/>
+    </row>
+    <row r="493" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C493" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C150" s="4"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="4"/>
-    </row>
-    <row r="151" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="4" t="s">
+      <c r="D493" s="4"/>
+      <c r="E493" s="5"/>
+      <c r="F493" s="4"/>
+    </row>
+    <row r="494" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C494" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C151" s="4"/>
-      <c r="D151" s="5"/>
-      <c r="E151" s="4"/>
-    </row>
-    <row r="152" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="4" t="s">
+      <c r="D494" s="4"/>
+      <c r="E494" s="5"/>
+      <c r="F494" s="4"/>
+    </row>
+    <row r="495" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C495" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C152" s="4"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="4"/>
-    </row>
-    <row r="153" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="4" t="s">
+      <c r="D495" s="4"/>
+      <c r="E495" s="5"/>
+      <c r="F495" s="4"/>
+    </row>
+    <row r="496" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C496" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C153" s="4"/>
-      <c r="D153" s="5"/>
-      <c r="E153" s="4"/>
-    </row>
-    <row r="154" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="4" t="s">
+      <c r="D496" s="4"/>
+      <c r="E496" s="5"/>
+      <c r="F496" s="4"/>
+    </row>
+    <row r="497" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C497" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C154" s="4"/>
-      <c r="D154" s="5"/>
-      <c r="E154" s="4"/>
-    </row>
-    <row r="155" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="4" t="s">
+      <c r="D497" s="4"/>
+      <c r="E497" s="5"/>
+      <c r="F497" s="4"/>
+    </row>
+    <row r="498" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C498" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C155" s="4"/>
-      <c r="D155" s="5"/>
-      <c r="E155" s="4"/>
-    </row>
-    <row r="156" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="4" t="s">
+      <c r="D498" s="4"/>
+      <c r="E498" s="5"/>
+      <c r="F498" s="4"/>
+    </row>
+    <row r="499" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C499" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C156" s="4"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="4"/>
-    </row>
-    <row r="157" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="4" t="s">
+      <c r="D499" s="4"/>
+      <c r="E499" s="5"/>
+      <c r="F499" s="4"/>
+    </row>
+    <row r="500" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C500" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C157" s="4"/>
-      <c r="D157" s="5"/>
-      <c r="E157" s="4"/>
-    </row>
-    <row r="158" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="4" t="s">
+      <c r="D500" s="4"/>
+      <c r="E500" s="5"/>
+      <c r="F500" s="4"/>
+    </row>
+    <row r="501" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C501" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C158" s="4"/>
-      <c r="D158" s="5"/>
-      <c r="E158" s="4"/>
-    </row>
-    <row r="159" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="4" t="s">
+      <c r="D501" s="4"/>
+      <c r="E501" s="5"/>
+      <c r="F501" s="4"/>
+    </row>
+    <row r="502" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C502" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C159" s="4"/>
-      <c r="D159" s="5"/>
-      <c r="E159" s="4"/>
-    </row>
-    <row r="160" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="4" t="s">
+      <c r="D502" s="4"/>
+      <c r="E502" s="5"/>
+      <c r="F502" s="4"/>
+    </row>
+    <row r="503" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C503" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C160" s="4"/>
-      <c r="D160" s="5"/>
-      <c r="E160" s="4"/>
-    </row>
-    <row r="161" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="4" t="s">
+      <c r="D503" s="4"/>
+      <c r="E503" s="5"/>
+      <c r="F503" s="4"/>
+    </row>
+    <row r="504" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C504" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C161" s="4"/>
-      <c r="D161" s="5"/>
-      <c r="E161" s="4"/>
-    </row>
-    <row r="162" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="4" t="s">
+      <c r="D504" s="4"/>
+      <c r="E504" s="5"/>
+      <c r="F504" s="4"/>
+    </row>
+    <row r="505" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C505" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C162" s="4"/>
-      <c r="D162" s="5"/>
-      <c r="E162" s="4"/>
-    </row>
-    <row r="163" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="4" t="s">
+      <c r="D505" s="4"/>
+      <c r="E505" s="5"/>
+      <c r="F505" s="4"/>
+    </row>
+    <row r="506" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C506" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C163" s="4"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="4"/>
-    </row>
-    <row r="164" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="4" t="s">
+      <c r="D506" s="4"/>
+      <c r="E506" s="5"/>
+      <c r="F506" s="4"/>
+    </row>
+    <row r="507" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C507" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C164" s="4"/>
-      <c r="D164" s="5"/>
-      <c r="E164" s="4"/>
-    </row>
-    <row r="165" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="4" t="s">
+      <c r="D507" s="4"/>
+      <c r="E507" s="5"/>
+      <c r="F507" s="4"/>
+    </row>
+    <row r="508" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C508" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C165" s="4"/>
-      <c r="D165" s="5"/>
-      <c r="E165" s="4"/>
-    </row>
-    <row r="166" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="4" t="s">
+      <c r="D508" s="4"/>
+      <c r="E508" s="5"/>
+      <c r="F508" s="4"/>
+    </row>
+    <row r="509" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C509" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C166" s="4"/>
-      <c r="D166" s="5"/>
-      <c r="E166" s="4"/>
-    </row>
-    <row r="167" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="4" t="s">
+      <c r="D509" s="4"/>
+      <c r="E509" s="5"/>
+      <c r="F509" s="4"/>
+    </row>
+    <row r="510" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C510" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C167" s="4"/>
-      <c r="D167" s="5"/>
-      <c r="E167" s="4"/>
-    </row>
-    <row r="168" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="4" t="s">
+      <c r="D510" s="4"/>
+      <c r="E510" s="5"/>
+      <c r="F510" s="4"/>
+    </row>
+    <row r="511" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C511" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C168" s="4"/>
-      <c r="D168" s="5"/>
-      <c r="E168" s="4"/>
-    </row>
-    <row r="169" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="4" t="s">
+      <c r="D511" s="4"/>
+      <c r="E511" s="5"/>
+      <c r="F511" s="4"/>
+    </row>
+    <row r="512" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C512" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C169" s="4"/>
-      <c r="D169" s="5"/>
-      <c r="E169" s="4"/>
-    </row>
-    <row r="170" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="4" t="s">
+      <c r="D512" s="4"/>
+      <c r="E512" s="5"/>
+      <c r="F512" s="4"/>
+    </row>
+    <row r="513" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C513" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C170" s="4"/>
-      <c r="D170" s="5"/>
-      <c r="E170" s="4"/>
-    </row>
-    <row r="171" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="4" t="s">
+      <c r="D513" s="4"/>
+      <c r="E513" s="5"/>
+      <c r="F513" s="4"/>
+    </row>
+    <row r="514" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C514" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C171" s="4"/>
-      <c r="D171" s="5"/>
-      <c r="E171" s="4"/>
-    </row>
-    <row r="172" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="4" t="s">
+      <c r="D514" s="4"/>
+      <c r="E514" s="5"/>
+      <c r="F514" s="4"/>
+    </row>
+    <row r="515" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C515" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C172" s="4"/>
-      <c r="D172" s="5"/>
-      <c r="E172" s="4"/>
-    </row>
-    <row r="173" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="4" t="s">
+      <c r="D515" s="4"/>
+      <c r="E515" s="5"/>
+      <c r="F515" s="4"/>
+    </row>
+    <row r="516" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C516" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C173" s="4"/>
-      <c r="D173" s="5"/>
-      <c r="E173" s="4"/>
-    </row>
-    <row r="174" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="4" t="s">
+      <c r="D516" s="4"/>
+      <c r="E516" s="5"/>
+      <c r="F516" s="4"/>
+    </row>
+    <row r="517" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C517" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C174" s="4"/>
-      <c r="D174" s="5"/>
-      <c r="E174" s="4"/>
-    </row>
-    <row r="175" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="4" t="s">
+      <c r="D517" s="4"/>
+      <c r="E517" s="5"/>
+      <c r="F517" s="4"/>
+    </row>
+    <row r="518" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C518" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C175" s="4"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="4"/>
-    </row>
-    <row r="176" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="4" t="s">
+      <c r="D518" s="4"/>
+      <c r="E518" s="5"/>
+      <c r="F518" s="4"/>
+    </row>
+    <row r="519" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C519" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C176" s="4"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="4"/>
-    </row>
-    <row r="177" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="4" t="s">
+      <c r="D519" s="4"/>
+      <c r="E519" s="5"/>
+      <c r="F519" s="4"/>
+    </row>
+    <row r="520" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C520" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C177" s="4"/>
-      <c r="D177" s="5"/>
-      <c r="E177" s="4"/>
-    </row>
-    <row r="178" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="4" t="s">
+      <c r="D520" s="4"/>
+      <c r="E520" s="5"/>
+      <c r="F520" s="4"/>
+    </row>
+    <row r="521" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C521" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C178" s="4"/>
-      <c r="D178" s="5"/>
-      <c r="E178" s="4"/>
-    </row>
-    <row r="179" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="4" t="s">
+      <c r="D521" s="4"/>
+      <c r="E521" s="5"/>
+      <c r="F521" s="4"/>
+    </row>
+    <row r="522" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C522" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C179" s="4"/>
-      <c r="D179" s="5"/>
-      <c r="E179" s="4"/>
-    </row>
-    <row r="180" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="4" t="s">
+      <c r="D522" s="4"/>
+      <c r="E522" s="5"/>
+      <c r="F522" s="4"/>
+    </row>
+    <row r="523" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C523" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C180" s="4"/>
-      <c r="D180" s="5"/>
-      <c r="E180" s="4"/>
-    </row>
-    <row r="181" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="4" t="s">
+      <c r="D523" s="4"/>
+      <c r="E523" s="5"/>
+      <c r="F523" s="4"/>
+    </row>
+    <row r="524" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C524" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C181" s="4"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="4"/>
-    </row>
-    <row r="182" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="4" t="s">
+      <c r="D524" s="4"/>
+      <c r="E524" s="5"/>
+      <c r="F524" s="4"/>
+    </row>
+    <row r="525" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C525" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C182" s="4"/>
-      <c r="D182" s="5"/>
-      <c r="E182" s="4"/>
-    </row>
-    <row r="183" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="4" t="s">
+      <c r="D525" s="4"/>
+      <c r="E525" s="5"/>
+      <c r="F525" s="4"/>
+    </row>
+    <row r="526" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C526" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C183" s="4"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="4"/>
-    </row>
-    <row r="184" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="4" t="s">
+      <c r="D526" s="4"/>
+      <c r="E526" s="5"/>
+      <c r="F526" s="4"/>
+    </row>
+    <row r="527" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C527" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C184" s="4"/>
-      <c r="D184" s="5"/>
-      <c r="E184" s="4"/>
-    </row>
-    <row r="185" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="4" t="s">
+      <c r="D527" s="4"/>
+      <c r="E527" s="5"/>
+      <c r="F527" s="4"/>
+    </row>
+    <row r="528" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C528" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C185" s="4"/>
-      <c r="D185" s="5"/>
-      <c r="E185" s="4"/>
-    </row>
-    <row r="186" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="4" t="s">
+      <c r="D528" s="4"/>
+      <c r="E528" s="5"/>
+      <c r="F528" s="4"/>
+    </row>
+    <row r="529" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C529" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C186" s="4"/>
-      <c r="D186" s="5"/>
-      <c r="E186" s="4"/>
-    </row>
-    <row r="187" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="4" t="s">
+      <c r="D529" s="4"/>
+      <c r="E529" s="5"/>
+      <c r="F529" s="4"/>
+    </row>
+    <row r="530" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C530" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C187" s="4"/>
-      <c r="D187" s="5"/>
-      <c r="E187" s="4"/>
-    </row>
-    <row r="188" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="4" t="s">
+      <c r="D530" s="4"/>
+      <c r="E530" s="5"/>
+      <c r="F530" s="4"/>
+    </row>
+    <row r="531" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C531" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C188" s="4"/>
-      <c r="D188" s="5"/>
-      <c r="E188" s="4"/>
-    </row>
-    <row r="189" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="4" t="s">
+      <c r="D531" s="4"/>
+      <c r="E531" s="5"/>
+      <c r="F531" s="4"/>
+    </row>
+    <row r="532" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C532" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C189" s="4"/>
-      <c r="D189" s="5"/>
-      <c r="E189" s="4"/>
-    </row>
-    <row r="190" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="4" t="s">
+      <c r="D532" s="4"/>
+      <c r="E532" s="5"/>
+      <c r="F532" s="4"/>
+    </row>
+    <row r="533" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C533" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C190" s="4"/>
-      <c r="D190" s="5"/>
-      <c r="E190" s="4"/>
-    </row>
-    <row r="191" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="4" t="s">
+      <c r="D533" s="4"/>
+      <c r="E533" s="5"/>
+      <c r="F533" s="4"/>
+    </row>
+    <row r="534" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C534" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C191" s="4"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="4"/>
-    </row>
-    <row r="192" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="4" t="s">
+      <c r="D534" s="4"/>
+      <c r="E534" s="5"/>
+      <c r="F534" s="4"/>
+    </row>
+    <row r="535" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C535" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C192" s="4"/>
-      <c r="D192" s="5"/>
-      <c r="E192" s="4"/>
-    </row>
-    <row r="193" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="4" t="s">
+      <c r="D535" s="4"/>
+      <c r="E535" s="5"/>
+      <c r="F535" s="4"/>
+    </row>
+    <row r="536" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C536" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C193" s="4"/>
-      <c r="D193" s="5"/>
-      <c r="E193" s="4"/>
-    </row>
-    <row r="194" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="4" t="s">
+      <c r="D536" s="4"/>
+      <c r="E536" s="5"/>
+      <c r="F536" s="4"/>
+    </row>
+    <row r="537" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C537" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C194" s="4"/>
-      <c r="D194" s="5"/>
-      <c r="E194" s="4"/>
-    </row>
-    <row r="195" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="4" t="s">
+      <c r="D537" s="4"/>
+      <c r="E537" s="5"/>
+      <c r="F537" s="4"/>
+    </row>
+    <row r="538" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C538" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C195" s="4"/>
-      <c r="D195" s="5"/>
-      <c r="E195" s="4"/>
-    </row>
-    <row r="196" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B196" s="4" t="s">
+      <c r="D538" s="4"/>
+      <c r="E538" s="5"/>
+      <c r="F538" s="4"/>
+    </row>
+    <row r="539" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C539" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C196" s="4"/>
-      <c r="D196" s="5"/>
-      <c r="E196" s="4"/>
-    </row>
-    <row r="197" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B197" s="4" t="s">
+      <c r="D539" s="4"/>
+      <c r="E539" s="5"/>
+      <c r="F539" s="4"/>
+    </row>
+    <row r="540" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C540" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C197" s="4"/>
-      <c r="D197" s="5"/>
-      <c r="E197" s="4"/>
-    </row>
-    <row r="198" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B198" s="4" t="s">
+      <c r="D540" s="4"/>
+      <c r="E540" s="5"/>
+      <c r="F540" s="4"/>
+    </row>
+    <row r="541" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C541" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C198" s="4"/>
-      <c r="D198" s="5"/>
-      <c r="E198" s="4"/>
-    </row>
-    <row r="199" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="4" t="s">
+      <c r="D541" s="4"/>
+      <c r="E541" s="5"/>
+      <c r="F541" s="4"/>
+    </row>
+    <row r="542" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C542" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C199" s="4"/>
-      <c r="D199" s="5"/>
-      <c r="E199" s="4"/>
-    </row>
-    <row r="200" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B200" s="4" t="s">
+      <c r="D542" s="4"/>
+      <c r="E542" s="5"/>
+      <c r="F542" s="4"/>
+    </row>
+    <row r="543" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C543" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C200" s="4"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="4"/>
-    </row>
-    <row r="201" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="4" t="s">
+      <c r="D543" s="4"/>
+      <c r="E543" s="5"/>
+      <c r="F543" s="4"/>
+    </row>
+    <row r="544" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C544" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C201" s="4"/>
-      <c r="D201" s="5"/>
-      <c r="E201" s="4"/>
-    </row>
-    <row r="202" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B202" s="4" t="s">
+      <c r="D544" s="4"/>
+      <c r="E544" s="5"/>
+      <c r="F544" s="4"/>
+    </row>
+    <row r="545" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C545" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C202" s="4"/>
-      <c r="D202" s="5"/>
-      <c r="E202" s="4"/>
-    </row>
-    <row r="203" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="4" t="s">
+      <c r="D545" s="4"/>
+      <c r="E545" s="5"/>
+      <c r="F545" s="4"/>
+    </row>
+    <row r="546" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C546" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C203" s="4"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="4"/>
-    </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D204" s="1"/>
-    </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D205" s="1"/>
-    </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D206" s="1"/>
-    </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D207" s="1"/>
-    </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D208" s="1"/>
+      <c r="D546" s="4"/>
+      <c r="E546" s="5"/>
+      <c r="F546" s="4"/>
+    </row>
+    <row r="547" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E547" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="32" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Control.xlsx
+++ b/Control.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\compartir\openlayers2_nvo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEE646A-C9E0-4FDA-A26B-CB74F00B7917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866FF221-E1A1-475E-887A-A3F8D7BEFA47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1245" windowWidth="25860" windowHeight="11295" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="220">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -824,9 +824,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -864,7 +864,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -970,7 +970,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1112,7 +1112,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1308,7 +1308,9 @@
         <v>12</v>
       </c>
       <c r="D15" s="10"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F15" s="7"/>
       <c r="G15" s="5">
         <v>1</v>
@@ -1319,7 +1321,9 @@
         <v>13</v>
       </c>
       <c r="D16" s="10"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F16" s="7"/>
       <c r="G16" s="5">
         <v>1</v>
@@ -1330,7 +1334,9 @@
         <v>14</v>
       </c>
       <c r="D17" s="10"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F17" s="7"/>
       <c r="G17" s="5">
         <v>1</v>
@@ -1341,7 +1347,9 @@
         <v>136</v>
       </c>
       <c r="D18" s="10"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F18" s="7"/>
       <c r="G18" s="5">
         <v>1</v>
@@ -1352,7 +1360,9 @@
         <v>15</v>
       </c>
       <c r="D19" s="10"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F19" s="7"/>
       <c r="G19" s="5">
         <v>1</v>
@@ -1363,7 +1373,9 @@
         <v>16</v>
       </c>
       <c r="D20" s="10"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F20" s="7"/>
       <c r="G20" s="5">
         <v>1</v>
@@ -1374,7 +1386,9 @@
         <v>17</v>
       </c>
       <c r="D21" s="10"/>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F21" s="7"/>
       <c r="G21" s="5">
         <v>1</v>
@@ -1385,7 +1399,9 @@
         <v>137</v>
       </c>
       <c r="D22" s="10"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="5">
         <v>1</v>
@@ -1396,7 +1412,9 @@
         <v>138</v>
       </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="4"/>
+      <c r="E23" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="5">
         <v>1</v>
@@ -1407,7 +1425,9 @@
         <v>18</v>
       </c>
       <c r="D24" s="10"/>
-      <c r="E24" s="4"/>
+      <c r="E24" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5">
         <v>1</v>
@@ -1418,7 +1438,9 @@
         <v>19</v>
       </c>
       <c r="D25" s="10"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5">
         <v>1</v>
@@ -1428,46 +1450,66 @@
       <c r="C26" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="G26" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="G27" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="G28" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="29" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="G29" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="G30" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
@@ -1476,7 +1518,7 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
@@ -1485,7 +1527,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="5"/>
     </row>
     <row r="33" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
@@ -1494,7 +1536,7 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="4" t="s">
@@ -1503,7 +1545,7 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="G34" s="5"/>
     </row>
     <row r="35" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
@@ -1512,7 +1554,7 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="G35" s="5"/>
     </row>
     <row r="36" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">
@@ -1521,7 +1563,7 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="G36" s="5"/>
     </row>
     <row r="37" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
@@ -1530,7 +1572,7 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="G37" s="5"/>
     </row>
     <row r="38" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
@@ -1543,7 +1585,7 @@
       <c r="F38" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="G38" s="4"/>
+      <c r="G38" s="5"/>
     </row>
     <row r="39" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
@@ -1552,7 +1594,7 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+      <c r="G39" s="5"/>
     </row>
     <row r="40" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
@@ -1561,7 +1603,7 @@
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="G40" s="5"/>
     </row>
     <row r="41" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
@@ -1570,7 +1612,7 @@
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
+      <c r="G41" s="5"/>
     </row>
     <row r="42" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
@@ -1579,7 +1621,7 @@
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="5"/>
     </row>
     <row r="43" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="4" t="s">
@@ -1588,7 +1630,7 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
+      <c r="G43" s="5"/>
     </row>
     <row r="44" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
@@ -1597,7 +1639,7 @@
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="G44" s="5"/>
     </row>
     <row r="45" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
@@ -1606,7 +1648,7 @@
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
+      <c r="G45" s="5"/>
     </row>
     <row r="46" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
@@ -1615,7 +1657,7 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="G46" s="5"/>
     </row>
     <row r="47" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
@@ -1624,7 +1666,7 @@
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
+      <c r="G47" s="5"/>
     </row>
     <row r="48" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
@@ -1633,7 +1675,7 @@
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="G48" s="5"/>
     </row>
     <row r="49" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="4" t="s">
@@ -1642,7 +1684,7 @@
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="G49" s="5"/>
     </row>
     <row r="50" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="4" t="s">
@@ -1651,7 +1693,7 @@
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="G50" s="5"/>
     </row>
     <row r="51" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="4" t="s">
@@ -1660,7 +1702,7 @@
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="G51" s="5"/>
     </row>
     <row r="52" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="4" t="s">
@@ -1669,7 +1711,7 @@
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="G52" s="5"/>
     </row>
     <row r="53" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="4" t="s">
@@ -1678,7 +1720,7 @@
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
+      <c r="G53" s="5"/>
     </row>
     <row r="54" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
@@ -1687,7 +1729,7 @@
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="G54" s="5"/>
     </row>
     <row r="55" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
@@ -1696,7 +1738,7 @@
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
+      <c r="G55" s="5"/>
     </row>
     <row r="56" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
@@ -1705,7 +1747,7 @@
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="G56" s="5"/>
     </row>
     <row r="57" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
@@ -1714,7 +1756,7 @@
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
+      <c r="G57" s="5"/>
     </row>
     <row r="58" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="4" t="s">
@@ -1723,7 +1765,7 @@
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
+      <c r="G58" s="5"/>
     </row>
     <row r="59" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="4" t="s">
@@ -1732,7 +1774,7 @@
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
+      <c r="G59" s="5"/>
     </row>
     <row r="60" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
@@ -1741,7 +1783,7 @@
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
+      <c r="G60" s="5"/>
     </row>
     <row r="61" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="4" t="s">
@@ -1750,7 +1792,7 @@
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
+      <c r="G61" s="5"/>
     </row>
     <row r="62" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="4" t="s">
@@ -1759,7 +1801,7 @@
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
+      <c r="G62" s="5"/>
     </row>
     <row r="63" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="4" t="s">
@@ -1768,7 +1810,7 @@
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
+      <c r="G63" s="5"/>
     </row>
     <row r="64" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="4" t="s">
@@ -1777,7 +1819,7 @@
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
+      <c r="G64" s="5"/>
     </row>
     <row r="65" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="4" t="s">
@@ -1786,7 +1828,7 @@
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
+      <c r="G65" s="5"/>
     </row>
     <row r="66" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="4" t="s">
@@ -1795,7 +1837,7 @@
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
+      <c r="G66" s="5"/>
     </row>
     <row r="67" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="4" t="s">
@@ -1804,7 +1846,7 @@
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
+      <c r="G67" s="5"/>
     </row>
     <row r="68" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="4" t="s">
@@ -1813,7 +1855,7 @@
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="G68" s="5"/>
     </row>
     <row r="69" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
@@ -1822,7 +1864,7 @@
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
+      <c r="G69" s="5"/>
     </row>
     <row r="70" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
@@ -1831,7 +1873,7 @@
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
+      <c r="G70" s="5"/>
     </row>
     <row r="71" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
@@ -1840,7 +1882,7 @@
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
+      <c r="G71" s="5"/>
     </row>
     <row r="72" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
@@ -1849,7 +1891,7 @@
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
+      <c r="G72" s="5"/>
     </row>
     <row r="73" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="4" t="s">
@@ -1858,7 +1900,7 @@
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
+      <c r="G73" s="5"/>
     </row>
     <row r="74" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
@@ -1867,7 +1909,7 @@
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
+      <c r="G74" s="5"/>
     </row>
     <row r="75" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
@@ -1876,7 +1918,7 @@
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
+      <c r="G75" s="5"/>
     </row>
     <row r="76" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
@@ -1885,7 +1927,7 @@
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
+      <c r="G76" s="5"/>
     </row>
     <row r="77" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
@@ -1894,7 +1936,7 @@
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
+      <c r="G77" s="5"/>
     </row>
     <row r="78" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="4" t="s">
@@ -1903,7 +1945,7 @@
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
+      <c r="G78" s="5"/>
     </row>
     <row r="79" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
@@ -1912,7 +1954,7 @@
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
+      <c r="G79" s="5"/>
     </row>
     <row r="80" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
@@ -1921,7 +1963,7 @@
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
+      <c r="G80" s="5"/>
     </row>
     <row r="81" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
@@ -1930,7 +1972,7 @@
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
+      <c r="G81" s="5"/>
     </row>
     <row r="82" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
@@ -1939,7 +1981,7 @@
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
+      <c r="G82" s="5"/>
     </row>
     <row r="83" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="4" t="s">
@@ -1948,7 +1990,7 @@
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
+      <c r="G83" s="5"/>
     </row>
     <row r="84" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="4" t="s">
@@ -1957,7 +1999,7 @@
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
+      <c r="G84" s="5"/>
     </row>
     <row r="85" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="4" t="s">
@@ -1966,7 +2008,7 @@
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
+      <c r="G85" s="5"/>
     </row>
     <row r="86" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
@@ -1975,7 +2017,7 @@
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
+      <c r="G86" s="5"/>
     </row>
     <row r="87" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="4" t="s">
@@ -1984,7 +2026,7 @@
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
+      <c r="G87" s="5"/>
     </row>
     <row r="88" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="4" t="s">
@@ -1993,7 +2035,7 @@
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
+      <c r="G88" s="5"/>
     </row>
     <row r="89" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C89" s="4" t="s">
@@ -2002,7 +2044,7 @@
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
+      <c r="G89" s="5"/>
     </row>
     <row r="90" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="4" t="s">
@@ -2011,7 +2053,7 @@
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
+      <c r="G90" s="5"/>
     </row>
     <row r="91" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="4" t="s">
@@ -2020,7 +2062,7 @@
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
+      <c r="G91" s="5"/>
     </row>
     <row r="92" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C92" s="4" t="s">
@@ -2029,7 +2071,7 @@
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
+      <c r="G92" s="5"/>
     </row>
     <row r="93" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="4" t="s">
@@ -2038,7 +2080,7 @@
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
+      <c r="G93" s="5"/>
     </row>
     <row r="94" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
@@ -2047,7 +2089,7 @@
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
+      <c r="G94" s="5"/>
     </row>
     <row r="95" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
@@ -2056,7 +2098,7 @@
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
+      <c r="G95" s="5"/>
     </row>
     <row r="96" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
@@ -2065,7 +2107,7 @@
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
+      <c r="G96" s="5"/>
     </row>
     <row r="97" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
@@ -2074,7 +2116,7 @@
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
+      <c r="G97" s="5"/>
     </row>
     <row r="98" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
@@ -2083,7 +2125,7 @@
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
+      <c r="G98" s="5"/>
     </row>
     <row r="99" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
@@ -2092,7 +2134,7 @@
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
+      <c r="G99" s="5"/>
     </row>
     <row r="100" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
@@ -2101,7 +2143,7 @@
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
+      <c r="G100" s="5"/>
     </row>
     <row r="101" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
@@ -2110,7 +2152,7 @@
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
+      <c r="G101" s="5"/>
     </row>
     <row r="102" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="4" t="s">
@@ -2119,7 +2161,7 @@
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
+      <c r="G102" s="5"/>
     </row>
     <row r="103" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="4" t="s">
@@ -2128,7 +2170,7 @@
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
+      <c r="G103" s="5"/>
     </row>
     <row r="104" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C104" s="4" t="s">
@@ -2137,7 +2179,7 @@
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
+      <c r="G104" s="5"/>
     </row>
     <row r="105" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C105" s="4" t="s">
@@ -2146,7 +2188,7 @@
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
+      <c r="G105" s="5"/>
     </row>
     <row r="106" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="4" t="s">
@@ -2155,7 +2197,7 @@
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
+      <c r="G106" s="5"/>
     </row>
     <row r="107" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C107" s="4" t="s">
@@ -2164,7 +2206,7 @@
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
+      <c r="G107" s="5"/>
     </row>
     <row r="108" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="4" t="s">
@@ -2173,7 +2215,7 @@
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
+      <c r="G108" s="5"/>
     </row>
     <row r="109" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C109" s="4" t="s">
@@ -2182,7 +2224,7 @@
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
+      <c r="G109" s="5"/>
     </row>
     <row r="110" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="4" t="s">
@@ -2191,7 +2233,7 @@
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
+      <c r="G110" s="5"/>
     </row>
     <row r="111" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C111" s="4" t="s">
@@ -2200,7 +2242,7 @@
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
+      <c r="G111" s="5"/>
     </row>
     <row r="112" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C112" s="4" t="s">
@@ -2209,7 +2251,7 @@
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
+      <c r="G112" s="5"/>
     </row>
     <row r="113" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="4" t="s">
@@ -2218,7 +2260,7 @@
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
+      <c r="G113" s="5"/>
     </row>
     <row r="114" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C114" s="4" t="s">
@@ -2227,7 +2269,7 @@
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
+      <c r="G114" s="5"/>
     </row>
     <row r="115" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C115" s="4" t="s">
@@ -2236,7 +2278,7 @@
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
-      <c r="G115" s="4"/>
+      <c r="G115" s="5"/>
     </row>
     <row r="116" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C116" s="4" t="s">
@@ -2245,7 +2287,7 @@
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
+      <c r="G116" s="5"/>
     </row>
     <row r="117" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C117" s="4" t="s">
@@ -2254,7 +2296,7 @@
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
+      <c r="G117" s="5"/>
     </row>
     <row r="118" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="4" t="s">
@@ -2263,7 +2305,7 @@
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
+      <c r="G118" s="5"/>
     </row>
     <row r="119" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" s="4" t="s">
@@ -2272,7 +2314,7 @@
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
+      <c r="G119" s="5"/>
     </row>
     <row r="120" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="4" t="s">
@@ -2281,7 +2323,7 @@
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
+      <c r="G120" s="5"/>
     </row>
     <row r="121" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="4" t="s">
@@ -2290,7 +2332,7 @@
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
+      <c r="G121" s="5"/>
     </row>
     <row r="122" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C122" s="4" t="s">
@@ -2299,7 +2341,7 @@
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
+      <c r="G122" s="5"/>
     </row>
     <row r="123" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="4" t="s">
@@ -2308,7 +2350,7 @@
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
-      <c r="G123" s="4"/>
+      <c r="G123" s="5"/>
     </row>
     <row r="124" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C124" s="4" t="s">
@@ -2317,7 +2359,7 @@
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
+      <c r="G124" s="5"/>
     </row>
     <row r="125" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="4" t="s">
@@ -2326,7 +2368,7 @@
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
+      <c r="G125" s="5"/>
     </row>
     <row r="126" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="4" t="s">
@@ -2335,7 +2377,7 @@
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
-      <c r="G126" s="4"/>
+      <c r="G126" s="5"/>
     </row>
     <row r="127" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C127" s="4" t="s">
@@ -2344,7 +2386,7 @@
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
+      <c r="G127" s="5"/>
     </row>
     <row r="128" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="4" t="s">
@@ -2353,7 +2395,7 @@
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
+      <c r="G128" s="5"/>
     </row>
     <row r="129" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C129" s="4" t="s">
@@ -2362,7 +2404,7 @@
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
-      <c r="G129" s="4"/>
+      <c r="G129" s="5"/>
     </row>
     <row r="130" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="4" t="s">
@@ -2371,7 +2413,7 @@
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
+      <c r="G130" s="5"/>
     </row>
     <row r="131" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="4" t="s">
@@ -2380,7 +2422,7 @@
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
+      <c r="G131" s="5"/>
     </row>
     <row r="132" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C132" s="4" t="s">
@@ -2389,7 +2431,7 @@
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
-      <c r="G132" s="4"/>
+      <c r="G132" s="5"/>
     </row>
     <row r="133" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C133" s="4" t="s">
@@ -2398,7 +2440,7 @@
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
+      <c r="G133" s="5"/>
     </row>
     <row r="134" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C134" s="4" t="s">
@@ -2409,7 +2451,7 @@
         <v>211</v>
       </c>
       <c r="F134" s="4"/>
-      <c r="G134" s="4">
+      <c r="G134" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866FF221-E1A1-475E-887A-A3F8D7BEFA47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA7B973-1BF2-48CF-96EA-2B30DCCA15C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="220">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -1515,19 +1515,27 @@
       <c r="C31" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F31" s="4"/>
-      <c r="G31" s="5"/>
+      <c r="G31" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="32" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="5"/>
+      <c r="G32" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="4" t="s">
@@ -1542,19 +1550,27 @@
       <c r="C34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F34" s="4"/>
-      <c r="G34" s="5"/>
+      <c r="G34" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="F35" s="4"/>
-      <c r="G35" s="5"/>
+      <c r="G35" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="4" t="s">

--- a/Control.xlsx
+++ b/Control.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.106.12.32\compartir\openlayers2_nvo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA7B973-1BF2-48CF-96EA-2B30DCCA15C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A35444-8D2A-423D-8223-496919639C5A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{119285BF-BAF3-43BB-BF3D-96AE8CA3F258}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="221">
   <si>
     <t>agregacgo.jsp</t>
   </si>
@@ -685,6 +685,9 @@
   </si>
   <si>
     <t>DESTINO</t>
+  </si>
+  <si>
+    <t>Se agrego una parte del codigo en el archivo java</t>
   </si>
 </sst>
 </file>
@@ -776,7 +779,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -803,6 +806,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1207,7 +1213,9 @@
       <c r="E7" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="7" t="s">
+        <v>220</v>
+      </c>
       <c r="G7" s="5">
         <v>1</v>
       </c>
@@ -1576,19 +1584,27 @@
       <c r="C36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="F36" s="4"/>
-      <c r="G36" s="5"/>
+      <c r="G36" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="37" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="F37" s="4"/>
-      <c r="G37" s="5"/>
+      <c r="G37" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="38" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="4" t="s">
@@ -1607,28 +1623,40 @@
       <c r="C39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="5"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="F40" s="4"/>
-      <c r="G40" s="5"/>
+      <c r="G40" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="F41" s="4"/>
-      <c r="G41" s="5"/>
+      <c r="G41" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="42" spans="3:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="4" t="s">
